--- a/i18n/lexique.xlsx
+++ b/i18n/lexique.xlsx
@@ -147,7 +147,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Pièces d’équipement : noms génériques choisis pour le site (Casque, Montre, Armure, Pantalon, Bague, Bâton / Helmet, Watch, Armor, Pants, Ring, Staff), car le jeu donne un nom différent à chaque pièce selon son niveau. « Veste » et « Canne » deviendront « Armure » et « Bâton » au branchement.</t>
+          <t xml:space="preserve">   Pièces d’équipement : noms génériques choisis pour le site (Casque, Montre, Manteau, Pantalon, Bague, Bâton / Helmet, Watch, Coat, Pants, Ring, Staff), car le jeu donne un nom différent à chaque pièce selon son niveau. « Veste » et « Canne » sont devenus « Manteau » et « Bâton ».</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.armure</t>
+          <t xml:space="preserve">game.bague</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
@@ -5483,24 +5483,19 @@
           <t xml:space="preserve">Pièce d’équipement</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Armure</t>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bague</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armor</t>
+          <t xml:space="preserve">Ring</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Nom générique choisi pour le site (les noms du jeu changent selon le niveau de la pièce)</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nouveau nom FR (aujourd’hui « Veste » sur le site, changera au branchement)</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
@@ -5517,7 +5512,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.bague</t>
+          <t xml:space="preserve">game.baton</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -5525,19 +5520,24 @@
           <t xml:space="preserve">Pièce d’équipement</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bague</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bâton</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ring</t>
+          <t xml:space="preserve">Staff</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Nom générique choisi pour le site (les noms du jeu changent selon le niveau de la pièce)</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nouveau nom FR (aujourd’hui « Canne » sur le site, changera au branchement)</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
@@ -5554,7 +5554,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.baton</t>
+          <t xml:space="preserve">game.casque</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
@@ -5562,14 +5562,14 @@
           <t xml:space="preserve">Pièce d’équipement</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bâton</t>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casque</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Staff</t>
+          <t xml:space="preserve">Helmet</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5577,14 +5577,9 @@
           <t xml:space="preserve">Nom générique choisi pour le site (les noms du jeu changent selon le niveau de la pièce)</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nouveau nom FR (aujourd’hui « Canne » sur le site, changera au branchement)</t>
-        </is>
-      </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talismans</t>
+          <t xml:space="preserve">Talismans, Équipement</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -5596,7 +5591,7 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.casque</t>
+          <t xml:space="preserve">game.manteau</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
@@ -5604,14 +5599,14 @@
           <t xml:space="preserve">Pièce d’équipement</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Casque</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manteau</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helmet</t>
+          <t xml:space="preserve">Coat</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -5619,9 +5614,14 @@
           <t xml:space="preserve">Nom générique choisi pour le site (les noms du jeu changent selon le niveau de la pièce)</t>
         </is>
       </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nouveau nom FR (aujourd’hui « Veste » sur le site, changera au branchement)</t>
+        </is>
+      </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talismans, Équipement</t>
+          <t xml:space="preserve">Talismans</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">

--- a/i18n/lexique.xlsx
+++ b/i18n/lexique.xlsx
@@ -9,8 +9,8 @@
     <sheet name="Hors traduction" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textes interface'!$A$3:$J$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termes du jeu'!$A$3:$H$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textes interface'!$A$3:$K$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termes du jeu'!$A$3:$J$106</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -140,127 +140,134 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Pour une nouvelle langue, ajoute une colonne (ES, DE, IT…). Une case vide = le site affichera le français.</t>
+          <t xml:space="preserve">   ES : termes du jeu relevés sur tes captures en espagnol (IMG_1284 à 1339) ; ceux qui n’y figurent pas sont des propositions en jaune, à vérifier en jeu.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Pièces d’équipement : noms génériques choisis pour le site (Casque, Montre, Manteau, Pantalon, Bague, Bâton / Helmet, Watch, Coat, Pants, Ring, Staff), car le jeu donne un nom différent à chaque pièce selon son niveau. « Veste » et « Canne » sont devenus « Manteau » et « Bâton ».</t>
+          <t xml:space="preserve">   Pour une nouvelle langue, ajoute une colonne (DE, IT…). Une case vide = le site affichera le français.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Bon à savoir : en anglais le T12 s’appelle « Exalted ». Les noms français T12 du site (« glorifié », Mur Indomptable, Phalange Méridienne…) correspondent au jeu en français (captures IMG_1043 à 1048).</t>
+          <t xml:space="preserve">   Pièces d’équipement : noms génériques choisis pour le site (Casque, Montre, Manteau, Pantalon, Bague, Bâton / Helmet, Watch, Coat, Pants, Ring, Staff), car le jeu donne un nom différent à chaque pièce selon son niveau. « Veste » et « Canne » sont devenus « Manteau » et « Bâton ».</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Ne modifie jamais la colonne « Clé » : c’est elle que le code utilisera. Tu peux corriger le texte FR, la traduction suivra la clé.</t>
+          <t xml:space="preserve">   Bon à savoir : en anglais le T12 s’appelle « Exalted ». Les noms français T12 du site (« glorifié », Mur Indomptable, Phalange Méridienne…) correspondent au jeu en français (captures IMG_1043 à 1048).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Les variables entre accolades ({name}, {level}, {to}…) sont remplacées par des valeurs : garde-les telles quelles, tu peux les déplacer dans la phrase.</t>
+          <t xml:space="preserve">2. Ne modifie jamais la colonne « Clé » : c’est elle que le code utilisera. Tu peux corriger le texte FR, la traduction suivra la clé.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Respecte la colonne « Longueur conseillée » pour les boutons et interrupteurs (affichage mobile).</t>
+          <t xml:space="preserve">3. Les variables entre accolades ({name}, {level}, {to}…) sont remplacées par des valeurs : garde-les telles quelles, tu peux les déplacer dans la phrase.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">4. Respecte la colonne « Longueur conseillée » pour les boutons et interrupteurs (affichage mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">5. Termes du jeu : reprends exactement le vocabulaire officiel du jeu dans chaque langue (change la langue du jeu pour les relever).</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Onglets</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Textes interface : 113 textes (titres, boutons, consignes, infobulles, textes lus par les lecteurs d’écran).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termes du jeu : 103 noms (ressources, troupes, pièces, raretés, recherches T11/T12, statistiques).</t>
+          <t xml:space="preserve">Textes interface : 113 textes (titres, boutons, consignes, infobulles, textes lus par les lecteurs d’écran).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formats et unités : 11 modèles (niveaux, abréviations, nombres, durées) — gérés par le code, à valider par langue.</t>
+          <t xml:space="preserve">Termes du jeu : 103 noms (ressources, troupes, pièces, raretés, recherches T11/T12, statistiques).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Formats et unités : 11 modèles (niveaux, abréviations, nombres, durées) — gérés par le code, à valider par langue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hors traduction : 11 éléments (noms de marque, codes, publicités factices).</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Colonnes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page : où le texte apparaît. Type : texte visible, infobulle, ou texte invisible lu par les lecteurs d’écran / description d’image (à traduire aussi, pour l’accessibilité).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vu à l’écran : « Non » = texte présent dans le code mais pas rencontré pendant le relevé. Ce sont surtout d’anciennes versions d’écrans restées dans le code (ex. « COÛT ÉQUIPEMENT », libellés à émoji) ou des messages conditionnels rares : inutile de les traduire en priorité, je confirmerai lesquels sont vraiment morts au branchement.</t>
+          <t xml:space="preserve">Page : où le texte apparaît. Type : texte visible, infobulle, ou texte invisible lu par les lecteurs d’écran / description d’image (à traduire aussi, pour l’accessibilité).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vu à l’écran : « Non » = texte présent dans le code mais pas rencontré pendant le relevé. Ce sont surtout d’anciennes versions d’écrans restées dans le code (ex. « COÛT ÉQUIPEMENT », libellés à émoji) ou des messages conditionnels rares : inutile de les traduire en priorité, je confirmerai lesquels sont vraiment morts au branchement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Source : fichier et ligne dans le code (pour moi, lors du branchement).</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Phase en cours</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Site entièrement verrouillé (visuels et fonctionnalités, desktop et mobile). Ce fichier ne modifie rien sur le site.</t>
         </is>
@@ -280,9 +287,10 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="48" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -331,15 +339,20 @@
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">ES</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Remarques</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Vu à l’écran</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
@@ -381,12 +394,17 @@
           <t xml:space="preserve">Chief Gear</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipo</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J4" s="0" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:24, app.js:181</t>
         </is>
@@ -428,12 +446,17 @@
           <t xml:space="preserve">Home</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inicio</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:22</t>
         </is>
@@ -475,12 +498,17 @@
           <t xml:space="preserve">Main navigation</t>
         </is>
       </c>
-      <c r="I6" s="0" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navegación principal</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J6" s="0" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:23</t>
         </is>
@@ -522,12 +550,17 @@
           <t xml:space="preserve">Chief Charms</t>
         </is>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Talismanes</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:24</t>
         </is>
@@ -564,12 +597,17 @@
           <t xml:space="preserve">Language</t>
         </is>
       </c>
-      <c r="I8" s="0" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idioma</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:26</t>
         </is>
@@ -606,12 +644,17 @@
           <t xml:space="preserve">WOS Companion crest</t>
         </is>
       </c>
-      <c r="I9" s="0" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emblema de WOS Companion</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:33</t>
         </is>
@@ -648,12 +691,17 @@
           <t xml:space="preserve">Plan. Progress.</t>
         </is>
       </c>
-      <c r="I10" s="0" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planifica. Progresa.</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:36</t>
         </is>
@@ -690,12 +738,17 @@
           <t xml:space="preserve">Survive the cold.</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sobrevive al frío.</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J11" s="0" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:36</t>
         </is>
@@ -732,12 +785,17 @@
           <t xml:space="preserve">Choose your goal and let</t>
         </is>
       </c>
-      <c r="I12" s="0" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elige tu objetivo y deja que</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:37</t>
         </is>
@@ -774,12 +832,17 @@
           <t xml:space="preserve">Companion work out the path.</t>
         </is>
       </c>
-      <c r="I13" s="0" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion calcule el camino.</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:37</t>
         </is>
@@ -816,12 +879,17 @@
           <t xml:space="preserve">Calculators</t>
         </is>
       </c>
-      <c r="I14" s="0" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculadoras</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J14" s="0" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:40</t>
         </is>
@@ -858,12 +926,17 @@
           <t xml:space="preserve">Chief Gear</t>
         </is>
       </c>
-      <c r="I15" s="0" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipo de Gobernador</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J15" s="0" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:42</t>
         </is>
@@ -900,12 +973,17 @@
           <t xml:space="preserve">Chief Charms</t>
         </is>
       </c>
-      <c r="I16" s="0" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Talismanes de Líder</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J16" s="0" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:43</t>
         </is>
@@ -942,12 +1020,17 @@
           <t xml:space="preserve">T11 Research</t>
         </is>
       </c>
-      <c r="I17" s="0" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigación T11</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J17" s="0" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:44</t>
         </is>
@@ -984,12 +1067,17 @@
           <t xml:space="preserve">T12 Research</t>
         </is>
       </c>
-      <c r="I18" s="0" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigación T12</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J18" s="0" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:45</t>
         </is>
@@ -1028,15 +1116,20 @@
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">EN DESARROLLO</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J19" s="0" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:46</t>
         </is>
@@ -1075,15 +1168,20 @@
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">★ PRÓXIMAMENTE ★</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J20" s="0" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:46</t>
         </is>
@@ -1120,12 +1218,17 @@
           <t xml:space="preserve">Hero VS Hero</t>
         </is>
       </c>
-      <c r="I21" s="0" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Héroe VS Héroe</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J21" s="0" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:46</t>
         </is>
@@ -1162,12 +1265,17 @@
           <t xml:space="preserve">Unofficial community tool · V1 data is isolated and versioned for auditing.</t>
         </is>
       </c>
-      <c r="I22" s="0" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herramienta comunitaria no oficial · Los datos V1 están aislados y versionados para auditoría.</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:48</t>
         </is>
@@ -1209,12 +1317,17 @@
           <t xml:space="preserve">Advertisement</t>
         </is>
       </c>
-      <c r="I23" s="0" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicidad</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J23" s="0" t="inlineStr">
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ads.js:7, ads.js:8</t>
         </is>
@@ -1251,12 +1364,17 @@
           <t xml:space="preserve">Set your current Furnace level and your target level.</t>
         </is>
       </c>
-      <c r="I24" s="0" t="inlineStr">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configura el nivel actual de tu Horno y el que quieres alcanzar.</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J24" s="0" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:53</t>
         </is>
@@ -1300,15 +1418,20 @@
       </c>
       <c r="H25" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">ACTUAL</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I25" s="0" t="inlineStr">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J25" s="0" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:55</t>
         </is>
@@ -1352,15 +1475,20 @@
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBJETIVO</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I26" s="0" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J26" s="0" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:57, app.js:154, app.js:172, app.js:244</t>
         </is>
@@ -1397,12 +1525,17 @@
           <t xml:space="preserve">Required buildings</t>
         </is>
       </c>
-      <c r="I27" s="0" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edificios requeridos</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J27" s="0" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:60</t>
         </is>
@@ -1439,12 +1572,17 @@
           <t xml:space="preserve">Buildings + Furnace total</t>
         </is>
       </c>
-      <c r="I28" s="0" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total edificios + Horno</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J28" s="0" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:61</t>
         </is>
@@ -1481,12 +1619,17 @@
           <t xml:space="preserve">Current Furnace</t>
         </is>
       </c>
-      <c r="I29" s="0" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horno actual</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J29" s="0" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:114</t>
         </is>
@@ -1525,15 +1668,20 @@
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Subniveles de</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="I30" s="0" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J30" s="0" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:129</t>
         </is>
@@ -1570,12 +1718,17 @@
           <t xml:space="preserve">Upgrade cost</t>
         </is>
       </c>
-      <c r="I31" s="0" t="inlineStr">
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costo de mejora</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J31" s="0" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, app.js:155, app.js:227</t>
         </is>
@@ -1617,12 +1770,17 @@
           <t xml:space="preserve">Target</t>
         </is>
       </c>
-      <c r="I32" s="0" t="inlineStr">
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Objetivo</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J32" s="0" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152, t12.js:310</t>
         </is>
@@ -1661,15 +1819,20 @@
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nv. {major}</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {major}</t>
         </is>
       </c>
-      <c r="I33" s="0" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J33" s="0" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:211, app.js:255</t>
         </is>
@@ -1708,15 +1871,20 @@
       </c>
       <c r="H34" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Subniveles de {x}</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I34" s="0" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J34" s="0" t="inlineStr">
+      <c r="K34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234</t>
         </is>
@@ -1753,12 +1921,17 @@
           <t xml:space="preserve">Sub-levels</t>
         </is>
       </c>
-      <c r="I35" s="0" t="inlineStr">
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subniveles</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J35" s="0" t="inlineStr">
+      <c r="K35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:323</t>
         </is>
@@ -1797,15 +1970,20 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horno {id}</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {id}</t>
         </is>
       </c>
-      <c r="I36" s="0" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J36" s="0" t="inlineStr">
+      <c r="K36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:74</t>
         </is>
@@ -1844,15 +2022,20 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{base}, subnivel {step} de {steps}</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {base}, {step}, {steps}</t>
         </is>
       </c>
-      <c r="I37" s="0" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J37" s="0" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:88</t>
         </is>
@@ -1894,12 +2077,17 @@
           <t xml:space="preserve">Close</t>
         </is>
       </c>
-      <c r="I38" s="0" t="inlineStr">
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrar</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J38" s="0" t="inlineStr">
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:92, app.js:105</t>
         </is>
@@ -1941,12 +2129,17 @@
           <t xml:space="preserve">Current</t>
         </is>
       </c>
-      <c r="I39" s="0" t="inlineStr">
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actual</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J39" s="0" t="inlineStr">
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:310</t>
         </is>
@@ -1990,15 +2183,20 @@
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paso {step}/{x}</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {step}, {x}</t>
         </is>
       </c>
-      <c r="I40" s="0" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J40" s="0" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234</t>
         </is>
@@ -2042,15 +2240,20 @@
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{label} · barra vacía</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {label}</t>
         </is>
       </c>
-      <c r="I41" s="0" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J41" s="0" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234</t>
         </is>
@@ -2092,12 +2295,17 @@
           <t xml:space="preserve">Choose this level without a sub-level</t>
         </is>
       </c>
-      <c r="I42" s="0" t="inlineStr">
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elegir este nivel sin subnivel</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J42" s="0" t="inlineStr">
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234</t>
         </is>
@@ -2141,15 +2349,20 @@
       </c>
       <c r="H43" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">SUBNIVEL</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I43" s="0" t="inlineStr">
+      <c r="J43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J43" s="0" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234, app.js:255</t>
         </is>
@@ -2193,15 +2406,20 @@
       </c>
       <c r="H44" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paso {step}/{steps}</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {step}, {steps}</t>
         </is>
       </c>
-      <c r="I44" s="0" t="inlineStr">
+      <c r="J44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J44" s="0" t="inlineStr">
+      <c r="K44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:255</t>
         </is>
@@ -2245,15 +2463,20 @@
       </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">NIVEL</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I45" s="0" t="inlineStr">
+      <c r="J45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J45" s="0" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:143</t>
         </is>
@@ -2290,12 +2513,17 @@
           <t xml:space="preserve">Set the current level and target of each piece.</t>
         </is>
       </c>
-      <c r="I46" s="0" t="inlineStr">
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configura el nivel actual y el objetivo de cada pieza.</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J46" s="0" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:67</t>
         </is>
@@ -2332,12 +2560,17 @@
           <t xml:space="preserve">Select all</t>
         </is>
       </c>
-      <c r="I47" s="0" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seleccionar todo</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J47" s="0" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:69</t>
         </is>
@@ -2376,15 +2609,20 @@
       </c>
       <c r="H48" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name} · TALISMÁN {x}</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {x}</t>
         </is>
       </c>
-      <c r="I48" s="0" t="inlineStr">
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J48" s="0" t="inlineStr">
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153</t>
         </is>
@@ -2428,15 +2666,20 @@
       </c>
       <c r="H49" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nivel {x}</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I49" s="0" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J49" s="0" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153</t>
         </is>
@@ -2480,15 +2723,20 @@
       </c>
       <c r="H50" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nivel {value}</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {value}</t>
         </is>
       </c>
-      <c r="I50" s="0" t="inlineStr">
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J50" s="0" t="inlineStr">
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:154, app.js:172</t>
         </is>
@@ -2527,15 +2775,20 @@
       </c>
       <c r="H51" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paso {step} de {steps}</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {step}, {steps}</t>
         </is>
       </c>
-      <c r="I51" s="0" t="inlineStr">
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J51" s="0" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:198</t>
         </is>
@@ -2579,15 +2832,20 @@
       </c>
       <c r="H52" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nivel {major}</t>
+        </is>
+      </c>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {major}</t>
         </is>
       </c>
-      <c r="I52" s="0" t="inlineStr">
+      <c r="J52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J52" s="0" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:207, app.js:255</t>
         </is>
@@ -2626,15 +2884,20 @@
       </c>
       <c r="H53" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name} · Talismán {x}</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {x}</t>
         </is>
       </c>
-      <c r="I53" s="0" t="inlineStr">
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J53" s="0" t="inlineStr">
+      <c r="K53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:245</t>
         </is>
@@ -2673,15 +2936,20 @@
       </c>
       <c r="H54" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nivel {major}, paso {step} de {steps}</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {major}, {step}, {steps}</t>
         </is>
       </c>
-      <c r="I54" s="0" t="inlineStr">
+      <c r="J54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J54" s="0" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:255</t>
         </is>
@@ -2720,15 +2988,20 @@
       </c>
       <c r="H55" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Subniveles del nivel {major}</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {major}</t>
         </is>
       </c>
-      <c r="I55" s="0" t="inlineStr">
+      <c r="J55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J55" s="0" t="inlineStr">
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:255</t>
         </is>
@@ -2765,12 +3038,17 @@
           <t xml:space="preserve">Set the current level and target of each of the 18 charms.</t>
         </is>
       </c>
-      <c r="I56" s="0" t="inlineStr">
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configura el nivel actual y el objetivo de cada uno de los 18 talismanes.</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J56" s="0" t="inlineStr">
+      <c r="K56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:74</t>
         </is>
@@ -2812,12 +3090,17 @@
           <t xml:space="preserve">Decrease target</t>
         </is>
       </c>
-      <c r="I57" s="0" t="inlineStr">
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bajar objetivo</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J57" s="0" t="inlineStr">
+      <c r="K57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:100</t>
         </is>
@@ -2859,12 +3142,17 @@
           <t xml:space="preserve">Increase target</t>
         </is>
       </c>
-      <c r="I58" s="0" t="inlineStr">
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subir objetivo</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J58" s="0" t="inlineStr">
+      <c r="K58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:100</t>
         </is>
@@ -2906,12 +3194,17 @@
           <t xml:space="preserve">Apply</t>
         </is>
       </c>
-      <c r="I59" s="0" t="inlineStr">
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aplicar</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J59" s="0" t="inlineStr">
+      <c r="K59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:103</t>
         </is>
@@ -2948,12 +3241,17 @@
           <t xml:space="preserve">T11 Research</t>
         </is>
       </c>
-      <c r="I60" s="0" t="inlineStr">
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigación T11</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J60" s="0" t="inlineStr">
+      <c r="K60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:81</t>
         </is>
@@ -2990,12 +3288,17 @@
           <t xml:space="preserve">Choose your troop, then tap a research to set its current level and target.</t>
         </is>
       </c>
-      <c r="I61" s="0" t="inlineStr">
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elige tu tropa y toca una investigación para ajustar su nivel actual y su objetivo.</t>
+        </is>
+      </c>
+      <c r="J61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J61" s="0" t="inlineStr">
+      <c r="K61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:81</t>
         </is>
@@ -3032,12 +3335,17 @@
           <t xml:space="preserve">Troop</t>
         </is>
       </c>
-      <c r="I62" s="0" t="inlineStr">
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tropa</t>
+        </is>
+      </c>
+      <c r="J62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J62" s="0" t="inlineStr">
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:82</t>
         </is>
@@ -3074,12 +3382,17 @@
           <t xml:space="preserve">Reset</t>
         </is>
       </c>
-      <c r="I63" s="0" t="inlineStr">
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reiniciar</t>
+        </is>
+      </c>
+      <c r="J63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J63" s="0" t="inlineStr">
+      <c r="K63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:88</t>
         </is>
@@ -3116,12 +3429,17 @@
           <t xml:space="preserve">Max all</t>
         </is>
       </c>
-      <c r="I64" s="0" t="inlineStr">
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todo al máx.</t>
+        </is>
+      </c>
+      <c r="J64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J64" s="0" t="inlineStr">
+      <c r="K64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:88, t12.js:297</t>
         </is>
@@ -3158,12 +3476,17 @@
           <t xml:space="preserve">Set the current level of this research and your target level.</t>
         </is>
       </c>
-      <c r="I65" s="0" t="inlineStr">
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajusta el nivel actual de esta investigación y el nivel que quieres alcanzar.</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J65" s="0" t="inlineStr">
+      <c r="K65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:95</t>
         </is>
@@ -3205,12 +3528,17 @@
           <t xml:space="preserve">Decrease current level</t>
         </is>
       </c>
-      <c r="I66" s="0" t="inlineStr">
+      <c r="H66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bajar nivel actual</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J66" s="0" t="inlineStr">
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:98</t>
         </is>
@@ -3252,12 +3580,17 @@
           <t xml:space="preserve">Increase current level</t>
         </is>
       </c>
-      <c r="I67" s="0" t="inlineStr">
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subir nivel actual</t>
+        </is>
+      </c>
+      <c r="J67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J67" s="0" t="inlineStr">
+      <c r="K67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:98</t>
         </is>
@@ -3301,15 +3634,20 @@
       </c>
       <c r="H68" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">, bloqueada</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="I68" s="0" t="inlineStr">
+      <c r="J68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J68" s="0" t="inlineStr">
+      <c r="K68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:101, t12.js:210, t12.js:289</t>
         </is>
@@ -3353,15 +3691,20 @@
       </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name}: nivel {from} de {max}{x}{x}</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {from}, {max}, {x}</t>
         </is>
       </c>
-      <c r="I69" s="0" t="inlineStr">
+      <c r="J69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J69" s="0" t="inlineStr">
+      <c r="K69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:101, t12.js:210</t>
         </is>
@@ -3398,12 +3741,17 @@
           <t xml:space="preserve">Research cost</t>
         </is>
       </c>
-      <c r="I70" s="0" t="inlineStr">
+      <c r="H70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costo de investigación</t>
+        </is>
+      </c>
+      <c r="J70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J70" s="0" t="inlineStr">
+      <c r="K70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:133, t12.js:373</t>
         </is>
@@ -3447,15 +3795,20 @@
       </c>
       <c r="H71" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name}: nivel {from} de 5{x}</t>
+        </is>
+      </c>
+      <c r="I71" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {from}, {x}</t>
         </is>
       </c>
-      <c r="I71" s="0" t="inlineStr">
+      <c r="J71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J71" s="0" t="inlineStr">
+      <c r="K71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:289</t>
         </is>
@@ -3489,15 +3842,20 @@
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">objetivo {to}</t>
+        </is>
+      </c>
+      <c r="I72" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau ajouté après « niveau … sur … »</t>
         </is>
       </c>
-      <c r="I72" s="0" t="inlineStr">
+      <c r="J72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J72" s="0" t="inlineStr">
+      <c r="K72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:101, t12.js:210</t>
         </is>
@@ -3536,15 +3894,20 @@
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name} Nv. {min}</t>
+        </is>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ligne de prérequis (précédée de ✓ ou ✗)</t>
         </is>
       </c>
-      <c r="I73" s="0" t="inlineStr">
+      <c r="J73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J73" s="0" t="inlineStr">
+      <c r="K73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:169, t12.js:406</t>
         </is>
@@ -3588,15 +3951,20 @@
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REQUISITOS{x}</t>
+        </is>
+      </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I74" s="0" t="inlineStr">
+      <c r="J74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J74" s="0" t="inlineStr">
+      <c r="K74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:168, t12.js:405</t>
         </is>
@@ -3633,12 +4001,17 @@
           <t xml:space="preserve">T12 Research</t>
         </is>
       </c>
-      <c r="I75" s="0" t="inlineStr">
+      <c r="H75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigación T12</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J75" s="0" t="inlineStr">
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:109</t>
         </is>
@@ -3675,12 +4048,17 @@
           <t xml:space="preserve">Choose your troop, unlock the Exalted unit, then progress its tree.</t>
         </is>
       </c>
-      <c r="I76" s="0" t="inlineStr">
+      <c r="H76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elige tu tropa, desbloquea la unidad sublime y luego haz progresar su árbol.</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J76" s="0" t="inlineStr">
+      <c r="K76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:109</t>
         </is>
@@ -3717,12 +4095,17 @@
           <t xml:space="preserve">Section</t>
         </is>
       </c>
-      <c r="I77" s="0" t="inlineStr">
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sección</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J77" s="0" t="inlineStr">
+      <c r="K77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:115</t>
         </is>
@@ -3764,12 +4147,17 @@
           <t xml:space="preserve">Unlock</t>
         </is>
       </c>
-      <c r="I78" s="0" t="inlineStr">
+      <c r="H78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Desbloqueo</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J78" s="0" t="inlineStr">
+      <c r="K78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:116</t>
         </is>
@@ -3811,12 +4199,17 @@
           <t xml:space="preserve">Tree</t>
         </is>
       </c>
-      <c r="I79" s="0" t="inlineStr">
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Árbol</t>
+        </is>
+      </c>
+      <c r="J79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J79" s="0" t="inlineStr">
+      <c r="K79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:117</t>
         </is>
@@ -3853,12 +4246,17 @@
           <t xml:space="preserve">Unit not unlocked yet: you can still set the tree to plan ahead.</t>
         </is>
       </c>
-      <c r="I80" s="0" t="inlineStr">
+      <c r="H80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad aún no desbloqueada: puedes ajustar el árbol para planificar.</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J80" s="0" t="inlineStr">
+      <c r="K80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:119</t>
         </is>
@@ -3900,12 +4298,17 @@
           <t xml:space="preserve">Minus 10</t>
         </is>
       </c>
-      <c r="I81" s="0" t="inlineStr">
+      <c r="H81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Menos 10</t>
+        </is>
+      </c>
+      <c r="J81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J81" s="0" t="inlineStr">
+      <c r="K81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:132</t>
         </is>
@@ -3947,12 +4350,17 @@
           <t xml:space="preserve">Plus 10</t>
         </is>
       </c>
-      <c r="I82" s="0" t="inlineStr">
+      <c r="H82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Más 10</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J82" s="0" t="inlineStr">
+      <c r="K82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:132</t>
         </is>
@@ -3991,15 +4399,20 @@
       </c>
       <c r="H83" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">desbloqueada</t>
+        </is>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="I83" s="0" t="inlineStr">
+      <c r="J83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J83" s="0" t="inlineStr">
+      <c r="K83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:207</t>
         </is>
@@ -4038,15 +4451,20 @@
       </c>
       <c r="H84" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">aún no desbloqueada</t>
+        </is>
+      </c>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="I84" s="0" t="inlineStr">
+      <c r="J84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J84" s="0" t="inlineStr">
+      <c r="K84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:207</t>
         </is>
@@ -4090,15 +4508,20 @@
       </c>
       <c r="H85" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">de la Infantería</t>
+        </is>
+      </c>
+      <c r="I85" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="I85" s="0" t="inlineStr">
+      <c r="J85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J85" s="0" t="inlineStr">
+      <c r="K85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:293</t>
         </is>
@@ -4142,15 +4565,20 @@
       </c>
       <c r="H86" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{label}: menos 1</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {label}</t>
         </is>
       </c>
-      <c r="I86" s="0" t="inlineStr">
+      <c r="J86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J86" s="0" t="inlineStr">
+      <c r="K86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:297</t>
         </is>
@@ -4194,15 +4622,20 @@
       </c>
       <c r="H87" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{label}: más 1</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {label}</t>
         </is>
       </c>
-      <c r="I87" s="0" t="inlineStr">
+      <c r="J87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J87" s="0" t="inlineStr">
+      <c r="K87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:297</t>
         </is>
@@ -4246,15 +4679,20 @@
       </c>
       <c r="H88" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{label}: nivel máx.</t>
+        </is>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {label}</t>
         </is>
       </c>
-      <c r="I88" s="0" t="inlineStr">
+      <c r="J88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J88" s="0" t="inlineStr">
+      <c r="K88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:297</t>
         </is>
@@ -4291,12 +4729,17 @@
           <t xml:space="preserve">Total unlock cost</t>
         </is>
       </c>
-      <c r="I89" s="0" t="inlineStr">
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costo total del desbloqueo</t>
+        </is>
+      </c>
+      <c r="J89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J89" s="0" t="inlineStr">
+      <c r="K89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:373</t>
         </is>
@@ -4335,15 +4778,20 @@
       </c>
       <c r="H90" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{x} desbloqueada</t>
+        </is>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I90" s="0" t="inlineStr">
+      <c r="J90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J90" s="0" t="inlineStr">
+      <c r="K90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:406</t>
         </is>
@@ -4380,12 +4828,17 @@
           <t xml:space="preserve">{done}/5 pieces</t>
         </is>
       </c>
-      <c r="I91" s="0" t="inlineStr">
+      <c r="H91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{done}/5 piezas</t>
+        </is>
+      </c>
+      <c r="J91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="J91" s="0" t="inlineStr">
+      <c r="K91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:300</t>
         </is>
@@ -4419,15 +4872,20 @@
       </c>
       <c r="H92" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">HASTA EL NIVEL {to}</t>
+        </is>
+      </c>
+      <c r="I92" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {to}</t>
         </is>
       </c>
-      <c r="I92" s="0" t="inlineStr">
+      <c r="J92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J92" s="0" t="inlineStr">
+      <c r="K92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:168, t12.js:405</t>
         </is>
@@ -4461,15 +4919,20 @@
       </c>
       <c r="H93" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">del {x}</t>
+        </is>
+      </c>
+      <c r="I93" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I93" s="0" t="inlineStr">
+      <c r="J93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J93" s="0" t="inlineStr">
+      <c r="K93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:293</t>
         </is>
@@ -4501,12 +4964,17 @@
           <t xml:space="preserve">The research tree is available</t>
         </is>
       </c>
-      <c r="I94" s="0" t="inlineStr">
+      <c r="H94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El árbol de investigación está disponible</t>
+        </is>
+      </c>
+      <c r="J94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J94" s="0" t="inlineStr">
+      <c r="K94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:302</t>
         </is>
@@ -4538,12 +5006,17 @@
           <t xml:space="preserve">Only enter your Chief’s current state.</t>
         </is>
       </c>
-      <c r="I95" s="0" t="inlineStr">
+      <c r="H95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indica solo el estado actual de tu Gobernador.</t>
+        </is>
+      </c>
+      <c r="J95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J95" s="0" t="inlineStr">
+      <c r="K95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:142</t>
         </is>
@@ -4577,15 +5050,20 @@
       </c>
       <c r="H96" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">EQUIPO ACTUAL</t>
+        </is>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I96" s="0" t="inlineStr">
+      <c r="J96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J96" s="0" t="inlineStr">
+      <c r="K96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:142</t>
         </is>
@@ -4617,12 +5095,17 @@
           <t xml:space="preserve">Choose a level</t>
         </is>
       </c>
-      <c r="I97" s="0" t="inlineStr">
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elegir un nivel</t>
+        </is>
+      </c>
+      <c r="J97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J97" s="0" t="inlineStr">
+      <c r="K97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:143</t>
         </is>
@@ -4654,12 +5137,17 @@
           <t xml:space="preserve">Target Furnace</t>
         </is>
       </c>
-      <c r="I98" s="0" t="inlineStr">
+      <c r="H98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horno objetivo</t>
+        </is>
+      </c>
+      <c r="J98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J98" s="0" t="inlineStr">
+      <c r="K98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:114</t>
         </is>
@@ -4693,15 +5181,20 @@
       </c>
       <c r="H99" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Abrir {name}, nivel actual {x}</t>
+        </is>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {x}</t>
         </is>
       </c>
-      <c r="I99" s="0" t="inlineStr">
+      <c r="J99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J99" s="0" t="inlineStr">
+      <c r="K99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:151</t>
         </is>
@@ -4733,12 +5226,17 @@
           <t xml:space="preserve">⚙️ Alloy</t>
         </is>
       </c>
-      <c r="I100" s="0" t="inlineStr">
+      <c r="H100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚙️ Aleación</t>
+        </is>
+      </c>
+      <c r="J100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J100" s="0" t="inlineStr">
+      <c r="K100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -4770,12 +5268,17 @@
           <t xml:space="preserve">✨ Polishing</t>
         </is>
       </c>
-      <c r="I101" s="0" t="inlineStr">
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✨ Pulidora</t>
+        </is>
+      </c>
+      <c r="J101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J101" s="0" t="inlineStr">
+      <c r="K101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -4807,12 +5310,17 @@
           <t xml:space="preserve">📜 Plans</t>
         </is>
       </c>
-      <c r="I102" s="0" t="inlineStr">
+      <c r="H102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📜 Planos</t>
+        </is>
+      </c>
+      <c r="J102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J102" s="0" t="inlineStr">
+      <c r="K102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -4844,12 +5352,17 @@
           <t xml:space="preserve">🟠 Lunar Amber</t>
         </is>
       </c>
-      <c r="I103" s="0" t="inlineStr">
+      <c r="H103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🟠 Ámbar lunar</t>
+        </is>
+      </c>
+      <c r="J103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J103" s="0" t="inlineStr">
+      <c r="K103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -4883,15 +5396,20 @@
       </c>
       <c r="H104" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">COSTO DEL EQUIPO</t>
+        </is>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I104" s="0" t="inlineStr">
+      <c r="J104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J104" s="0" t="inlineStr">
+      <c r="K104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -4923,12 +5441,17 @@
           <t xml:space="preserve">Targets for the 6 pieces</t>
         </is>
       </c>
-      <c r="I105" s="0" t="inlineStr">
+      <c r="H105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Objetivos de las 6 piezas</t>
+        </is>
+      </c>
+      <c r="J105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J105" s="0" t="inlineStr">
+      <c r="K105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -4962,15 +5485,20 @@
       </c>
       <c r="H106" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">COSTO DE TALISMANES</t>
+        </is>
+      </c>
+      <c r="I106" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I106" s="0" t="inlineStr">
+      <c r="J106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J106" s="0" t="inlineStr">
+      <c r="K106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152, app.js:155</t>
         </is>
@@ -5002,12 +5530,17 @@
           <t xml:space="preserve">Targets for the 18 charms</t>
         </is>
       </c>
-      <c r="I107" s="0" t="inlineStr">
+      <c r="H107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Objetivos de los 18 talismanes</t>
+        </is>
+      </c>
+      <c r="J107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J107" s="0" t="inlineStr">
+      <c r="K107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -5039,12 +5572,17 @@
           <t xml:space="preserve">📘 Guides</t>
         </is>
       </c>
-      <c r="I108" s="0" t="inlineStr">
+      <c r="H108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📘 Guías</t>
+        </is>
+      </c>
+      <c r="J108" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J108" s="0" t="inlineStr">
+      <c r="K108" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152, app.js:155</t>
         </is>
@@ -5076,12 +5614,17 @@
           <t xml:space="preserve">💠 Designs</t>
         </is>
       </c>
-      <c r="I109" s="0" t="inlineStr">
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💠 Planos</t>
+        </is>
+      </c>
+      <c r="J109" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J109" s="0" t="inlineStr">
+      <c r="K109" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152, app.js:155</t>
         </is>
@@ -5115,15 +5658,20 @@
       </c>
       <c r="H110" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">NIVEL ACTUAL</t>
+        </is>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="I110" s="0" t="inlineStr">
+      <c r="J110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J110" s="0" t="inlineStr">
+      <c r="K110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153, app.js:154, app.js:172, app.js:244</t>
         </is>
@@ -5155,12 +5703,17 @@
           <t xml:space="preserve">Set each pair directly</t>
         </is>
       </c>
-      <c r="I111" s="0" t="inlineStr">
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configura cada par directamente</t>
+        </is>
+      </c>
+      <c r="J111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J111" s="0" t="inlineStr">
+      <c r="K111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153</t>
         </is>
@@ -5192,12 +5745,17 @@
           <t xml:space="preserve">current › target</t>
         </is>
       </c>
-      <c r="I112" s="0" t="inlineStr">
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual › objetivo</t>
+        </is>
+      </c>
+      <c r="J112" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J112" s="0" t="inlineStr">
+      <c r="K112" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153</t>
         </is>
@@ -5231,15 +5789,20 @@
       </c>
       <c r="H113" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Talismán {x}</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I113" s="0" t="inlineStr">
+      <c r="J113" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J113" s="0" t="inlineStr">
+      <c r="K113" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:154, app.js:156, app.js:172</t>
         </is>
@@ -5271,12 +5834,17 @@
           <t xml:space="preserve">Required resources</t>
         </is>
       </c>
-      <c r="I114" s="0" t="inlineStr">
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recursos necesarios</t>
+        </is>
+      </c>
+      <c r="J114" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J114" s="0" t="inlineStr">
+      <c r="K114" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -5310,15 +5878,20 @@
       </c>
       <c r="H115" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Subnivel {step} de {x}</t>
+        </is>
+      </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {step}, {x}</t>
         </is>
       </c>
-      <c r="I115" s="0" t="inlineStr">
+      <c r="J115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J115" s="0" t="inlineStr">
+      <c r="K115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:197</t>
         </is>
@@ -5350,19 +5923,24 @@
           <t xml:space="preserve">Choose the sub-level</t>
         </is>
       </c>
-      <c r="I116" s="0" t="inlineStr">
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elegir el subnivel</t>
+        </is>
+      </c>
+      <c r="J116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="J116" s="0" t="inlineStr">
+      <c r="K116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:310</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J116"/>
+  <autoFilter ref="A3:K116"/>
 </worksheet>
 </file>
 
@@ -5373,10 +5951,12 @@
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5421,15 +6001,25 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">ES</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiabilité ES</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Remarques</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pages où il apparaît</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
@@ -5461,12 +6051,22 @@
           <t xml:space="preserve">Officiel — WOSForge</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horno</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Accueil, Chaudière, Menu</t>
         </is>
       </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:8</t>
         </is>
@@ -5498,12 +6098,22 @@
           <t xml:space="preserve">Nom générique choisi pour le site (les noms du jeu changent selon le niveau de la pièce)</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anillo</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction de Bague)</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -5537,15 +6147,25 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bastón</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction de Bâton)</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nouveau nom FR (aujourd’hui « Canne » sur le site, changera au branchement)</t>
         </is>
       </c>
-      <c r="G6" s="0" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="H6" s="0" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -5577,12 +6197,22 @@
           <t xml:space="preserve">Nom générique choisi pour le site (les noms du jeu changent selon le niveau de la pièce)</t>
         </is>
       </c>
-      <c r="G7" s="0" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casco</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction de Casque)</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans, Équipement</t>
         </is>
       </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -5616,15 +6246,25 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Abrigo</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction de Manteau)</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nouveau nom FR (aujourd’hui « Veste » sur le site, changera au branchement)</t>
         </is>
       </c>
-      <c r="G8" s="0" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -5656,12 +6296,22 @@
           <t xml:space="preserve">Nom générique choisi pour le site (les noms du jeu changent selon le niveau de la pièce)</t>
         </is>
       </c>
-      <c r="G9" s="0" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reloj</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction de Montre)</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="H9" s="0" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -5693,12 +6343,22 @@
           <t xml:space="preserve">Nom générique choisi pour le site (les noms du jeu changent selon le niveau de la pièce)</t>
         </is>
       </c>
-      <c r="G10" s="0" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pantalones</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction de Pantalon)</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -5732,15 +6392,25 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Legendario{x}</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="G11" s="0" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:9</t>
         </is>
@@ -5772,12 +6442,22 @@
           <t xml:space="preserve">Officiel — WOSForge</t>
         </is>
       </c>
-      <c r="G12" s="0" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mítico</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:4, data.js:131</t>
         </is>
@@ -5811,15 +6491,25 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mítico{x}</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="G13" s="0" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="H13" s="0" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:7</t>
         </is>
@@ -5853,15 +6543,25 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Poco común{x}</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="G14" s="0" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="H14" s="0" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:3</t>
         </is>
@@ -5895,15 +6595,25 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Raro{x}</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="G15" s="0" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="H15" s="0" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:4</t>
         </is>
@@ -5935,12 +6645,22 @@
           <t xml:space="preserve">Officiel — WOSForge</t>
         </is>
       </c>
-      <c r="G16" s="0" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Épico</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="H16" s="0" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:4, data.js:123</t>
         </is>
@@ -5974,15 +6694,25 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Épico{x}</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="G17" s="0" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="H17" s="0" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:5</t>
         </is>
@@ -6014,12 +6744,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G18" s="0" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armamento sublime</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H18" s="0" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -6051,12 +6791,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blindaje fundido</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H19" s="0" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:27</t>
         </is>
@@ -6088,12 +6838,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G20" s="0" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura Ardiente</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H20" s="0" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:49</t>
         </is>
@@ -6125,12 +6885,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G21" s="0" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura de Cristal</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H21" s="0" t="inlineStr">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:50</t>
         </is>
@@ -6162,12 +6932,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G22" s="0" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senda de guerra sublime</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H22" s="0" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -6199,12 +6979,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G23" s="0" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escudo de Llamas</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H23" s="0" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:48</t>
         </is>
@@ -6236,12 +7026,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G24" s="0" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escudos fundidos</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H24" s="0" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:27</t>
         </is>
@@ -6273,12 +7073,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G25" s="0" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cadencia sublime</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H25" s="0" t="inlineStr">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -6310,12 +7120,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G26" s="0" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yelmo sublime</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H26" s="0" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -6347,12 +7167,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G27" s="0" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cascos fundidos</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H27" s="0" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:28</t>
         </is>
@@ -6384,12 +7214,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G28" s="0" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga Ardiente</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H28" s="0" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:49</t>
         </is>
@@ -6421,12 +7261,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G29" s="0" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cota de malla sublime</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H29" s="0" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -6458,12 +7308,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G30" s="0" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corona de guerra sublime</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H30" s="0" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -6495,12 +7355,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G31" s="0" t="inlineStr">
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supremacía solar</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H31" s="0" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:37</t>
         </is>
@@ -6532,12 +7402,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G32" s="0" t="inlineStr">
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entrenamiento de Infanterías Sublimes</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H32" s="0" t="inlineStr">
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:35</t>
         </is>
@@ -6569,12 +7449,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G33" s="0" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entrenamiento de Lanceros Sublimes</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H33" s="0" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:35</t>
         </is>
@@ -6606,12 +7496,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G34" s="0" t="inlineStr">
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entrenamiento de Tiradores Sublimes</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H34" s="0" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:35</t>
         </is>
@@ -6645,15 +7545,25 @@
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Entrenamiento de {unit} Helios</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
         </is>
       </c>
-      <c r="G35" s="0" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H35" s="0" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:61</t>
         </is>
@@ -6687,15 +7597,25 @@
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Entrenamiento de Infantería Helios</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H36" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Forme élidée produite par le code pour l’infanterie</t>
         </is>
       </c>
-      <c r="G36" s="0" t="inlineStr">
+      <c r="I36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H36" s="0" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:61</t>
         </is>
@@ -6727,12 +7647,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G37" s="0" t="inlineStr">
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escuadrón de Llamas</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H37" s="0" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:53</t>
         </is>
@@ -6764,12 +7694,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G38" s="0" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Travesía sublime</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H38" s="0" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -6801,12 +7741,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G39" s="0" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flecha de Cristal</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H39" s="0" t="inlineStr">
+      <c r="J39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:50</t>
         </is>
@@ -6838,12 +7788,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G40" s="0" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ataque de Llamas</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H40" s="0" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:48</t>
         </is>
@@ -6875,12 +7835,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G41" s="0" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empuñadura fundida</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H41" s="0" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:29</t>
         </is>
@@ -6912,12 +7882,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G42" s="0" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guardia fundido</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H42" s="0" t="inlineStr">
+      <c r="J42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:27</t>
         </is>
@@ -6949,12 +7929,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G43" s="0" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hombreras sublimes</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H43" s="0" t="inlineStr">
+      <c r="J43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -6986,12 +7976,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G44" s="0" t="inlineStr">
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guardián Ardiente</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H44" s="0" t="inlineStr">
+      <c r="J44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:49</t>
         </is>
@@ -7023,12 +8023,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G45" s="0" t="inlineStr">
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espadas fundidas</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H45" s="0" t="inlineStr">
+      <c r="J45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:27</t>
         </is>
@@ -7060,12 +8070,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G46" s="0" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lanza fundida</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H46" s="0" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:28</t>
         </is>
@@ -7097,12 +8117,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G47" s="0" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lanza Ardiente</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H47" s="0" t="inlineStr">
+      <c r="J47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:49</t>
         </is>
@@ -7134,12 +8164,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G48" s="0" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legión de Llamas</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H48" s="0" t="inlineStr">
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:56</t>
         </is>
@@ -7171,12 +8211,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G49" s="0" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manto sublime</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H49" s="0" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -7208,12 +8258,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G50" s="0" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muro indomable</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H50" s="0" t="inlineStr">
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:31</t>
         </is>
@@ -7245,12 +8305,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G51" s="0" t="inlineStr">
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falange meridiana</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H51" s="0" t="inlineStr">
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:31</t>
         </is>
@@ -7282,12 +8352,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G52" s="0" t="inlineStr">
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pica sublime</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H52" s="0" t="inlineStr">
+      <c r="J52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -7319,12 +8399,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G53" s="0" t="inlineStr">
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bastión sublime</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H53" s="0" t="inlineStr">
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -7356,12 +8446,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G54" s="0" t="inlineStr">
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primeros Auxilios de Infanterías Sublimes</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H54" s="0" t="inlineStr">
+      <c r="J54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:34</t>
         </is>
@@ -7393,12 +8493,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G55" s="0" t="inlineStr">
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primeros Auxilios de Lanceros Sublimes</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H55" s="0" t="inlineStr">
+      <c r="J55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:34</t>
         </is>
@@ -7430,12 +8540,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G56" s="0" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primeros Auxilios de Tiradores Sublimes</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H56" s="0" t="inlineStr">
+      <c r="J56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:34</t>
         </is>
@@ -7467,12 +8587,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G57" s="0" t="inlineStr">
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protección de Cristal</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H57" s="0" t="inlineStr">
+      <c r="J57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:50</t>
         </is>
@@ -7504,12 +8634,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G58" s="0" t="inlineStr">
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protección de Llamas</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H58" s="0" t="inlineStr">
+      <c r="J58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:48</t>
         </is>
@@ -7541,12 +8681,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G59" s="0" t="inlineStr">
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avambrazo fundido</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H59" s="0" t="inlineStr">
+      <c r="J59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:28</t>
         </is>
@@ -7578,12 +8728,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G60" s="0" t="inlineStr">
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiro con precisión fundido</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H60" s="0" t="inlineStr">
+      <c r="J60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:29</t>
         </is>
@@ -7615,12 +8775,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G61" s="0" t="inlineStr">
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curación de Infanterías Sublimes</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H61" s="0" t="inlineStr">
+      <c r="J61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:33</t>
         </is>
@@ -7652,12 +8822,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G62" s="0" t="inlineStr">
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curación de Lanceros Sublimes</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H62" s="0" t="inlineStr">
+      <c r="J62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:33</t>
         </is>
@@ -7689,12 +8869,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G63" s="0" t="inlineStr">
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curación de Tiradores Sublimes</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H63" s="0" t="inlineStr">
+      <c r="J63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:33</t>
         </is>
@@ -7726,12 +8916,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G64" s="0" t="inlineStr">
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tácticas fundidas</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H64" s="0" t="inlineStr">
+      <c r="J64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:28</t>
         </is>
@@ -7763,12 +8963,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G65" s="0" t="inlineStr">
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atuendo de guerra sublime</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H65" s="0" t="inlineStr">
+      <c r="J65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -7800,12 +9010,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G66" s="0" t="inlineStr">
+      <c r="F66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuego de estrella</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H66" s="0" t="inlineStr">
+      <c r="J66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:31</t>
         </is>
@@ -7837,12 +9057,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G67" s="0" t="inlineStr">
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disparo fundido</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H67" s="0" t="inlineStr">
+      <c r="J67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:29</t>
         </is>
@@ -7874,12 +9104,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G68" s="0" t="inlineStr">
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hacha de Llamas</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H68" s="0" t="inlineStr">
+      <c r="J68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:48</t>
         </is>
@@ -7911,12 +9151,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G69" s="0" t="inlineStr">
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trabuco sublime</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H69" s="0" t="inlineStr">
+      <c r="J69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -7948,12 +9198,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G70" s="0" t="inlineStr">
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visión de Cristal</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H70" s="0" t="inlineStr">
+      <c r="J70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:50</t>
         </is>
@@ -7985,12 +9245,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G71" s="0" t="inlineStr">
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Velo sublime</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H71" s="0" t="inlineStr">
+      <c r="J71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -8024,15 +9294,25 @@
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{unit} Helios</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H72" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
         </is>
       </c>
-      <c r="G72" s="0" t="inlineStr">
+      <c r="I72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H72" s="0" t="inlineStr">
+      <c r="J72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:59</t>
         </is>
@@ -8066,15 +9346,25 @@
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Primeros Auxilios de {unit} Helios</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H73" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
         </is>
       </c>
-      <c r="G73" s="0" t="inlineStr">
+      <c r="I73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H73" s="0" t="inlineStr">
+      <c r="J73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:62</t>
         </is>
@@ -8108,15 +9398,25 @@
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Curación de {unit} Helios</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H74" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
         </is>
       </c>
-      <c r="G74" s="0" t="inlineStr">
+      <c r="I74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="H74" s="0" t="inlineStr">
+      <c r="J74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:60</t>
         </is>
@@ -8148,12 +9448,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
-      <c r="G75" s="0" t="inlineStr">
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escamas fundidas</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H75" s="0" t="inlineStr">
+      <c r="J75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:29</t>
         </is>
@@ -8185,12 +9495,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G76" s="0" t="inlineStr">
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espaldarón sublime</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+        </is>
+      </c>
+      <c r="I76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H76" s="0" t="inlineStr">
+      <c r="J76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -8222,12 +9542,22 @@
           <t xml:space="preserve">Officiel — WOSForge</t>
         </is>
       </c>
-      <c r="G77" s="0" t="inlineStr">
+      <c r="F77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aceleradores</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
-      <c r="H77" s="0" t="inlineStr">
+      <c r="J77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t11.js:131, t12.js:370</t>
         </is>
@@ -8259,12 +9589,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G78" s="0" t="inlineStr">
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acero</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="H78" s="0" t="inlineStr">
+      <c r="J78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:126, t12.js:353, t12.js:365</t>
         </is>
@@ -8296,12 +9636,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G79" s="0" t="inlineStr">
+      <c r="F79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aleación endurecida</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="H79" s="0" t="inlineStr">
+      <c r="J79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -8333,12 +9683,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G80" s="0" t="inlineStr">
+      <c r="F80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ámbar lunar</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="H80" s="0" t="inlineStr">
+      <c r="J80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -8370,12 +9730,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G81" s="0" t="inlineStr">
+      <c r="F81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Madera</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
-      <c r="H81" s="0" t="inlineStr">
+      <c r="J81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t11.js:128, t12.js:367</t>
         </is>
@@ -8407,12 +9777,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G82" s="0" t="inlineStr">
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carbón</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
-      <c r="H82" s="0" t="inlineStr">
+      <c r="J82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t11.js:129, t12.js:368</t>
         </is>
@@ -8444,12 +9824,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G83" s="0" t="inlineStr">
+      <c r="F83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristal de Fuego</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière</t>
         </is>
       </c>
-      <c r="H83" s="0" t="inlineStr">
+      <c r="J83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149</t>
         </is>
@@ -8481,12 +9871,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G84" s="0" t="inlineStr">
+      <c r="F84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristal de fuego refinado</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T12</t>
         </is>
       </c>
-      <c r="H84" s="0" t="inlineStr">
+      <c r="J84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t12.js:352, t12.js:364</t>
         </is>
@@ -8518,12 +9918,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G85" s="0" t="inlineStr">
+      <c r="F85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hierro</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
-      <c r="H85" s="0" t="inlineStr">
+      <c r="J85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t11.js:130, t12.js:369</t>
         </is>
@@ -8555,12 +9965,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G86" s="0" t="inlineStr">
+      <c r="F86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fragmento de Cristal de Fuego</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="H86" s="0" t="inlineStr">
+      <c r="J86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:125, t12.js:351, t12.js:363</t>
         </is>
@@ -8592,12 +10012,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G87" s="0" t="inlineStr">
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guía de talismanes</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="H87" s="0" t="inlineStr">
+      <c r="J87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:223</t>
         </is>
@@ -8629,12 +10059,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1273) : la nourriture s’appelle Meat</t>
         </is>
       </c>
-      <c r="G88" s="0" t="inlineStr">
+      <c r="F88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carne</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière</t>
         </is>
       </c>
-      <c r="H88" s="0" t="inlineStr">
+      <c r="J88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149</t>
         </is>
@@ -8666,12 +10106,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G89" s="0" t="inlineStr">
+      <c r="F89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planos de diseño</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="H89" s="0" t="inlineStr">
+      <c r="J89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -8703,12 +10153,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G90" s="0" t="inlineStr">
+      <c r="F90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planos de talismán</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="H90" s="0" t="inlineStr">
+      <c r="J90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:224</t>
         </is>
@@ -8740,12 +10200,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G91" s="0" t="inlineStr">
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretos de talismanes</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="H91" s="0" t="inlineStr">
+      <c r="J91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:225</t>
         </is>
@@ -8777,12 +10247,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G92" s="0" t="inlineStr">
+      <c r="F92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solución pulidora</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="H92" s="0" t="inlineStr">
+      <c r="J92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -8814,12 +10294,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
-      <c r="G93" s="0" t="inlineStr">
+      <c r="F93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carne</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="H93" s="0" t="inlineStr">
+      <c r="J93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:127, t12.js:366</t>
         </is>
@@ -8851,12 +10341,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G94" s="0" t="inlineStr">
+      <c r="F94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ataque</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="H94" s="0" t="inlineStr">
+      <c r="J94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -8888,12 +10388,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G95" s="0" t="inlineStr">
+      <c r="F95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacidad de despliegue de tropas</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H95" s="0" t="inlineStr">
+      <c r="J95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -8925,12 +10435,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G96" s="0" t="inlineStr">
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacidad de despliegue de tropas</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H96" s="0" t="inlineStr">
+      <c r="J96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:293</t>
         </is>
@@ -8962,12 +10482,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G97" s="0" t="inlineStr">
+      <c r="F97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defensa</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="H97" s="0" t="inlineStr">
+      <c r="J97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -8999,12 +10529,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G98" s="0" t="inlineStr">
+      <c r="F98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Letalidad</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="H98" s="0" t="inlineStr">
+      <c r="J98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -9036,12 +10576,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G99" s="0" t="inlineStr">
+      <c r="F99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poder</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H99" s="0" t="inlineStr">
+      <c r="J99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:309</t>
         </is>
@@ -9073,12 +10623,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G100" s="0" t="inlineStr">
+      <c r="F100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salud</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="H100" s="0" t="inlineStr">
+      <c r="J100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -9110,12 +10670,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G101" s="0" t="inlineStr">
+      <c r="F101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infantería</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="H101" s="0" t="inlineStr">
+      <c r="J101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:83, app.js:151, app.js:152, app.js:153, app.js:199, app.js:204, app.js:206, data.js:8, data.js:46, t12.js:220</t>
         </is>
@@ -9147,12 +10717,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G102" s="0" t="inlineStr">
+      <c r="F102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infantería sublime</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H102" s="0" t="inlineStr">
+      <c r="J102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:12</t>
         </is>
@@ -9184,12 +10764,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G103" s="0" t="inlineStr">
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancero</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12, Talismans</t>
         </is>
       </c>
-      <c r="H103" s="0" t="inlineStr">
+      <c r="J103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:84, app.js:151, app.js:152, app.js:153, app.js:199, app.js:204, app.js:206, data.js:8, data.js:46, t12.js:220</t>
         </is>
@@ -9221,12 +10811,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G104" s="0" t="inlineStr">
+      <c r="F104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancero sublime</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H104" s="0" t="inlineStr">
+      <c r="J104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:12</t>
         </is>
@@ -9258,12 +10858,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
-      <c r="G105" s="0" t="inlineStr">
+      <c r="F105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tirador</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="H105" s="0" t="inlineStr">
+      <c r="J105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:85, data.js:8, data.js:46, t12.js:220</t>
         </is>
@@ -9295,19 +10905,29 @@
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="G106" s="0" t="inlineStr">
+      <c r="F106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tirador sublime</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="I106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="H106" s="0" t="inlineStr">
+      <c r="J106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H106"/>
+  <autoFilter ref="A3:J106"/>
 </worksheet>
 </file>
 

--- a/i18n/lexique.xlsx
+++ b/i18n/lexique.xlsx
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configura el nivel actual de tu Horno y el que quieres alcanzar.</t>
+          <t xml:space="preserve">Configura el nivel actual de tu Calefactor y el que quieres alcanzar.</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total edificios + Horno</t>
+          <t xml:space="preserve">Total edificios + Calefactor</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horno actual</t>
+          <t xml:space="preserve">Calefactor actual</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horno {id}</t>
+          <t xml:space="preserve">Calefactor {id}</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="H98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horno objetivo</t>
+          <t xml:space="preserve">Calefactor objetivo</t>
         </is>
       </c>
       <c r="J98" s="0" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horno</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Calefactor</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blindaje fundido</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Enchapado fundido</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I19" s="0" t="inlineStr">
@@ -7031,9 +7031,9 @@
           <t xml:space="preserve">Escudos fundidos</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrenamiento de Infanterías Sublimes</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Entrenamiento de Infantería Sublime</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I32" s="0" t="inlineStr">
@@ -7454,9 +7454,9 @@
           <t xml:space="preserve">Entrenamiento de Lanceros Sublimes</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I33" s="0" t="inlineStr">
@@ -7746,9 +7746,9 @@
           <t xml:space="preserve">Flecha de Cristal</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I39" s="0" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muro indomable</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Muro Indomable</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I50" s="0" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="F54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primeros Auxilios de Infanterías Sublimes</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Primeros Auxilios de Infantería Sublime</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I54" s="0" t="inlineStr">
@@ -8592,9 +8592,9 @@
           <t xml:space="preserve">Protección de Cristal</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I57" s="0" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curación de Infanterías Sublimes</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Curación de Infantería Sublime</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="I61" s="0" t="inlineStr">

--- a/i18n/lexique.xlsx
+++ b/i18n/lexique.xlsx
@@ -140,7 +140,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ES : termes du jeu relevés sur tes captures en espagnol (IMG_1284 à 1339) ; ceux qui n’y figurent pas sont des propositions en jaune, à vérifier en jeu.</t>
+          <t xml:space="preserve">   ES : termes du jeu relevés sur tes captures en espagnol (IMG_1284 à 1356). Les 15 pièces de déblocage T12 (en jaune) sont déduites des noms officiels anglais et français, faute de source espagnole.</t>
         </is>
       </c>
     </row>
@@ -6395,9 +6395,9 @@
           <t xml:space="preserve">Legendario{x}</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -6447,9 +6447,9 @@
           <t xml:space="preserve">Mítico</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
@@ -6494,9 +6494,9 @@
           <t xml:space="preserve">Mítico{x}</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -6546,9 +6546,9 @@
           <t xml:space="preserve">Poco común{x}</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -6598,9 +6598,9 @@
           <t xml:space="preserve">Raro{x}</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -6650,9 +6650,9 @@
           <t xml:space="preserve">Épico</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
@@ -6697,9 +6697,9 @@
           <t xml:space="preserve">Épico{x}</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I25" s="0" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yelmo sublime</t>
+          <t xml:space="preserve">Casco sublime</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travesía sublime</t>
+          <t xml:space="preserve">Excursión sublime</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hombreras sublimes</t>
+          <t xml:space="preserve">Hombrera sublime</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I43" s="0" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I49" s="0" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I52" s="0" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I53" s="0" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I65" s="0" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I69" s="0" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I71" s="0" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="I76" s="0" t="inlineStr">

--- a/i18n/lexique.xlsx
+++ b/i18n/lexique.xlsx
@@ -9,8 +9,8 @@
     <sheet name="Hors traduction" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textes interface'!$A$3:$K$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termes du jeu'!$A$3:$J$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textes interface'!$A$3:$L$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termes du jeu'!$A$3:$L$106</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -147,127 +147,134 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Pour une nouvelle langue, ajoute une colonne (DE, IT…). Une case vide = le site affichera le français.</t>
+          <t xml:space="preserve">   IT : textes d’interface traduits ; termes du jeu tous en proposition (jaune), faute de captures du jeu en italien.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Pièces d’équipement : noms génériques choisis pour le site (Casque, Montre, Manteau, Pantalon, Bague, Bâton / Helmet, Watch, Coat, Pants, Ring, Staff), car le jeu donne un nom différent à chaque pièce selon son niveau. « Veste » et « Canne » sont devenus « Manteau » et « Bâton ».</t>
+          <t xml:space="preserve">   Pour une nouvelle langue, ajoute une colonne (DE, PT…). Une case vide = le site affichera le français.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Bon à savoir : en anglais le T12 s’appelle « Exalted ». Les noms français T12 du site (« glorifié », Mur Indomptable, Phalange Méridienne…) correspondent au jeu en français (captures IMG_1043 à 1048).</t>
+          <t xml:space="preserve">   Pièces d’équipement : noms génériques choisis pour le site (Casque, Montre, Manteau, Pantalon, Bague, Bâton / Helmet, Watch, Coat, Pants, Ring, Staff), car le jeu donne un nom différent à chaque pièce selon son niveau. « Veste » et « Canne » sont devenus « Manteau » et « Bâton ».</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Ne modifie jamais la colonne « Clé » : c’est elle que le code utilisera. Tu peux corriger le texte FR, la traduction suivra la clé.</t>
+          <t xml:space="preserve">   Bon à savoir : en anglais le T12 s’appelle « Exalted ». Les noms français T12 du site (« glorifié », Mur Indomptable, Phalange Méridienne…) correspondent au jeu en français (captures IMG_1043 à 1048).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Les variables entre accolades ({name}, {level}, {to}…) sont remplacées par des valeurs : garde-les telles quelles, tu peux les déplacer dans la phrase.</t>
+          <t xml:space="preserve">2. Ne modifie jamais la colonne « Clé » : c’est elle que le code utilisera. Tu peux corriger le texte FR, la traduction suivra la clé.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Respecte la colonne « Longueur conseillée » pour les boutons et interrupteurs (affichage mobile).</t>
+          <t xml:space="preserve">3. Les variables entre accolades ({name}, {level}, {to}…) sont remplacées par des valeurs : garde-les telles quelles, tu peux les déplacer dans la phrase.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">4. Respecte la colonne « Longueur conseillée » pour les boutons et interrupteurs (affichage mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">5. Termes du jeu : reprends exactement le vocabulaire officiel du jeu dans chaque langue (change la langue du jeu pour les relever).</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Onglets</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Textes interface : 113 textes (titres, boutons, consignes, infobulles, textes lus par les lecteurs d’écran).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termes du jeu : 103 noms (ressources, troupes, pièces, raretés, recherches T11/T12, statistiques).</t>
+          <t xml:space="preserve">Textes interface : 113 textes (titres, boutons, consignes, infobulles, textes lus par les lecteurs d’écran).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formats et unités : 11 modèles (niveaux, abréviations, nombres, durées) — gérés par le code, à valider par langue.</t>
+          <t xml:space="preserve">Termes du jeu : 103 noms (ressources, troupes, pièces, raretés, recherches T11/T12, statistiques).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Formats et unités : 11 modèles (niveaux, abréviations, nombres, durées) — gérés par le code, à valider par langue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hors traduction : 11 éléments (noms de marque, codes, publicités factices).</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Colonnes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page : où le texte apparaît. Type : texte visible, infobulle, ou texte invisible lu par les lecteurs d’écran / description d’image (à traduire aussi, pour l’accessibilité).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vu à l’écran : « Non » = texte présent dans le code mais pas rencontré pendant le relevé. Ce sont surtout d’anciennes versions d’écrans restées dans le code (ex. « COÛT ÉQUIPEMENT », libellés à émoji) ou des messages conditionnels rares : inutile de les traduire en priorité, je confirmerai lesquels sont vraiment morts au branchement.</t>
+          <t xml:space="preserve">Page : où le texte apparaît. Type : texte visible, infobulle, ou texte invisible lu par les lecteurs d’écran / description d’image (à traduire aussi, pour l’accessibilité).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vu à l’écran : « Non » = texte présent dans le code mais pas rencontré pendant le relevé. Ce sont surtout d’anciennes versions d’écrans restées dans le code (ex. « COÛT ÉQUIPEMENT », libellés à émoji) ou des messages conditionnels rares : inutile de les traduire en priorité, je confirmerai lesquels sont vraiment morts au branchement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Source : fichier et ligne dans le code (pour moi, lors du branchement).</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Phase en cours</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Site entièrement verrouillé (visuels et fonctionnalités, desktop et mobile). Ce fichier ne modifie rien sur le site.</t>
         </is>
@@ -288,9 +295,10 @@
     <col min="6" max="6" width="48" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="48" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -344,15 +352,20 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Remarques</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Vu à l’écran</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
@@ -399,12 +412,17 @@
           <t xml:space="preserve">Equipo</t>
         </is>
       </c>
-      <c r="J4" s="0" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipaggiamento</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K4" s="0" t="inlineStr">
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:24, app.js:181</t>
         </is>
@@ -451,12 +469,17 @@
           <t xml:space="preserve">Inicio</t>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Home</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K5" s="0" t="inlineStr">
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:22</t>
         </is>
@@ -503,12 +526,17 @@
           <t xml:space="preserve">Navegación principal</t>
         </is>
       </c>
-      <c r="J6" s="0" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navigazione principale</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K6" s="0" t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:23</t>
         </is>
@@ -555,12 +583,17 @@
           <t xml:space="preserve">Talismanes</t>
         </is>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Talismani</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K7" s="0" t="inlineStr">
+      <c r="L7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:24</t>
         </is>
@@ -602,12 +635,17 @@
           <t xml:space="preserve">Idioma</t>
         </is>
       </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lingua</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K8" s="0" t="inlineStr">
+      <c r="L8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:26</t>
         </is>
@@ -649,12 +687,17 @@
           <t xml:space="preserve">Emblema de WOS Companion</t>
         </is>
       </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stemma di WOS Companion</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K9" s="0" t="inlineStr">
+      <c r="L9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:33</t>
         </is>
@@ -696,12 +739,17 @@
           <t xml:space="preserve">Planifica. Progresa.</t>
         </is>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pianifica. Progredisci.</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K10" s="0" t="inlineStr">
+      <c r="L10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:36</t>
         </is>
@@ -743,12 +791,17 @@
           <t xml:space="preserve">Sobrevive al frío.</t>
         </is>
       </c>
-      <c r="J11" s="0" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sopravvivi al gelo.</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K11" s="0" t="inlineStr">
+      <c r="L11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:36</t>
         </is>
@@ -790,12 +843,17 @@
           <t xml:space="preserve">Elige tu objetivo y deja que</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scegli il tuo obiettivo e lascia che</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K12" s="0" t="inlineStr">
+      <c r="L12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:37</t>
         </is>
@@ -837,12 +895,17 @@
           <t xml:space="preserve">Companion calcule el camino.</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion calcoli il percorso.</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K13" s="0" t="inlineStr">
+      <c r="L13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:37</t>
         </is>
@@ -884,12 +947,17 @@
           <t xml:space="preserve">Calculadoras</t>
         </is>
       </c>
-      <c r="J14" s="0" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcolatori</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K14" s="0" t="inlineStr">
+      <c r="L14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:40</t>
         </is>
@@ -931,12 +999,17 @@
           <t xml:space="preserve">Equipo de Gobernador</t>
         </is>
       </c>
-      <c r="J15" s="0" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipaggiamento Capo</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K15" s="0" t="inlineStr">
+      <c r="L15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:42</t>
         </is>
@@ -978,12 +1051,17 @@
           <t xml:space="preserve">Talismanes de Líder</t>
         </is>
       </c>
-      <c r="J16" s="0" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Talismani del Capo</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K16" s="0" t="inlineStr">
+      <c r="L16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:43</t>
         </is>
@@ -1025,12 +1103,17 @@
           <t xml:space="preserve">Investigación T11</t>
         </is>
       </c>
-      <c r="J17" s="0" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ricerca T11</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K17" s="0" t="inlineStr">
+      <c r="L17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:44</t>
         </is>
@@ -1072,12 +1155,17 @@
           <t xml:space="preserve">Investigación T12</t>
         </is>
       </c>
-      <c r="J18" s="0" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ricerca T12</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K18" s="0" t="inlineStr">
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:45</t>
         </is>
@@ -1121,15 +1209,20 @@
       </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">IN SVILUPPO</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J19" s="0" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K19" s="0" t="inlineStr">
+      <c r="L19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:46</t>
         </is>
@@ -1173,15 +1266,20 @@
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">★ IN ARRIVO ★</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J20" s="0" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K20" s="0" t="inlineStr">
+      <c r="L20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:46</t>
         </is>
@@ -1223,12 +1321,17 @@
           <t xml:space="preserve">Héroe VS Héroe</t>
         </is>
       </c>
-      <c r="J21" s="0" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eroe VS Eroe</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K21" s="0" t="inlineStr">
+      <c r="L21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:46</t>
         </is>
@@ -1270,12 +1373,17 @@
           <t xml:space="preserve">Herramienta comunitaria no oficial · Los datos V1 están aislados y versionados para auditoría.</t>
         </is>
       </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strumento non ufficiale della community · I dati V1 sono isolati e versionati per la verifica.</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K22" s="0" t="inlineStr">
+      <c r="L22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:48</t>
         </is>
@@ -1322,12 +1430,17 @@
           <t xml:space="preserve">Publicidad</t>
         </is>
       </c>
-      <c r="J23" s="0" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pubblicità</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K23" s="0" t="inlineStr">
+      <c r="L23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ads.js:7, ads.js:8</t>
         </is>
@@ -1369,12 +1482,17 @@
           <t xml:space="preserve">Configura el nivel actual de tu Calefactor y el que quieres alcanzar.</t>
         </is>
       </c>
-      <c r="J24" s="0" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imposta il livello attuale della tua Fornace e quello che vuoi raggiungere.</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K24" s="0" t="inlineStr">
+      <c r="L24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:53</t>
         </is>
@@ -1423,15 +1541,20 @@
       </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">ATTUALE</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J25" s="0" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K25" s="0" t="inlineStr">
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:55</t>
         </is>
@@ -1480,15 +1603,20 @@
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBIETTIVO</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J26" s="0" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K26" s="0" t="inlineStr">
+      <c r="L26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:57, app.js:154, app.js:172, app.js:244</t>
         </is>
@@ -1530,12 +1658,17 @@
           <t xml:space="preserve">Edificios requeridos</t>
         </is>
       </c>
-      <c r="J27" s="0" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edifici richiesti</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K27" s="0" t="inlineStr">
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:60</t>
         </is>
@@ -1577,12 +1710,17 @@
           <t xml:space="preserve">Total edificios + Calefactor</t>
         </is>
       </c>
-      <c r="J28" s="0" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Totale edifici + Fornace</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K28" s="0" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:61</t>
         </is>
@@ -1624,12 +1762,17 @@
           <t xml:space="preserve">Calefactor actual</t>
         </is>
       </c>
-      <c r="J29" s="0" t="inlineStr">
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fornace attuale</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K29" s="0" t="inlineStr">
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:114</t>
         </is>
@@ -1673,15 +1816,20 @@
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sottolivelli di</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="J30" s="0" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K30" s="0" t="inlineStr">
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:129</t>
         </is>
@@ -1723,12 +1871,17 @@
           <t xml:space="preserve">Costo de mejora</t>
         </is>
       </c>
-      <c r="J31" s="0" t="inlineStr">
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costo di potenziamento</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K31" s="0" t="inlineStr">
+      <c r="L31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, app.js:155, app.js:227</t>
         </is>
@@ -1775,12 +1928,17 @@
           <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
-      <c r="J32" s="0" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obiettivo</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K32" s="0" t="inlineStr">
+      <c r="L32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152, t12.js:310</t>
         </is>
@@ -1824,15 +1982,20 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Liv. {major}</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {major}</t>
         </is>
       </c>
-      <c r="J33" s="0" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K33" s="0" t="inlineStr">
+      <c r="L33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:211, app.js:255</t>
         </is>
@@ -1876,15 +2039,20 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sottolivelli di {x}</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="J34" s="0" t="inlineStr">
+      <c r="K34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K34" s="0" t="inlineStr">
+      <c r="L34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234</t>
         </is>
@@ -1926,12 +2094,17 @@
           <t xml:space="preserve">Subniveles</t>
         </is>
       </c>
-      <c r="J35" s="0" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sottolivelli</t>
+        </is>
+      </c>
+      <c r="K35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K35" s="0" t="inlineStr">
+      <c r="L35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:323</t>
         </is>
@@ -1975,15 +2148,20 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fornace {id}</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {id}</t>
         </is>
       </c>
-      <c r="J36" s="0" t="inlineStr">
+      <c r="K36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K36" s="0" t="inlineStr">
+      <c r="L36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:74</t>
         </is>
@@ -2027,15 +2205,20 @@
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{base}, sottolivello {step} di {steps}</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {base}, {step}, {steps}</t>
         </is>
       </c>
-      <c r="J37" s="0" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K37" s="0" t="inlineStr">
+      <c r="L37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:88</t>
         </is>
@@ -2082,12 +2265,17 @@
           <t xml:space="preserve">Cerrar</t>
         </is>
       </c>
-      <c r="J38" s="0" t="inlineStr">
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chiudi</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K38" s="0" t="inlineStr">
+      <c r="L38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:92, app.js:105</t>
         </is>
@@ -2134,12 +2322,17 @@
           <t xml:space="preserve">Actual</t>
         </is>
       </c>
-      <c r="J39" s="0" t="inlineStr">
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attuale</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K39" s="0" t="inlineStr">
+      <c r="L39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:310</t>
         </is>
@@ -2188,15 +2381,20 @@
       </c>
       <c r="I40" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fase {step}/{x}</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {step}, {x}</t>
         </is>
       </c>
-      <c r="J40" s="0" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K40" s="0" t="inlineStr">
+      <c r="L40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234</t>
         </is>
@@ -2245,15 +2443,20 @@
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{label} · barra vuota</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {label}</t>
         </is>
       </c>
-      <c r="J41" s="0" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K41" s="0" t="inlineStr">
+      <c r="L41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234</t>
         </is>
@@ -2300,12 +2503,17 @@
           <t xml:space="preserve">Elegir este nivel sin subnivel</t>
         </is>
       </c>
-      <c r="J42" s="0" t="inlineStr">
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scegli questo livello senza sottolivello</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K42" s="0" t="inlineStr">
+      <c r="L42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234</t>
         </is>
@@ -2354,15 +2562,20 @@
       </c>
       <c r="I43" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">SOTTOLIVELLO</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J43" s="0" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K43" s="0" t="inlineStr">
+      <c r="L43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:234, app.js:255</t>
         </is>
@@ -2411,15 +2624,20 @@
       </c>
       <c r="I44" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fase {step}/{steps}</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {step}, {steps}</t>
         </is>
       </c>
-      <c r="J44" s="0" t="inlineStr">
+      <c r="K44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K44" s="0" t="inlineStr">
+      <c r="L44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:255</t>
         </is>
@@ -2468,15 +2686,20 @@
       </c>
       <c r="I45" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">LIVELLO</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J45" s="0" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K45" s="0" t="inlineStr">
+      <c r="L45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:143</t>
         </is>
@@ -2518,12 +2741,17 @@
           <t xml:space="preserve">Configura el nivel actual y el objetivo de cada pieza.</t>
         </is>
       </c>
-      <c r="J46" s="0" t="inlineStr">
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imposta il livello attuale e l’obiettivo di ogni pezzo.</t>
+        </is>
+      </c>
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K46" s="0" t="inlineStr">
+      <c r="L46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:67</t>
         </is>
@@ -2565,12 +2793,17 @@
           <t xml:space="preserve">Seleccionar todo</t>
         </is>
       </c>
-      <c r="J47" s="0" t="inlineStr">
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seleziona tutto</t>
+        </is>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K47" s="0" t="inlineStr">
+      <c r="L47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:69</t>
         </is>
@@ -2614,15 +2847,20 @@
       </c>
       <c r="I48" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name} · TALISMANO {x}</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {x}</t>
         </is>
       </c>
-      <c r="J48" s="0" t="inlineStr">
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K48" s="0" t="inlineStr">
+      <c r="L48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153</t>
         </is>
@@ -2671,15 +2909,20 @@
       </c>
       <c r="I49" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Livello {x}</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="J49" s="0" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K49" s="0" t="inlineStr">
+      <c r="L49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153</t>
         </is>
@@ -2728,15 +2971,20 @@
       </c>
       <c r="I50" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Livello {value}</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {value}</t>
         </is>
       </c>
-      <c r="J50" s="0" t="inlineStr">
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K50" s="0" t="inlineStr">
+      <c r="L50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:154, app.js:172</t>
         </is>
@@ -2780,15 +3028,20 @@
       </c>
       <c r="I51" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fase {step} di {steps}</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {step}, {steps}</t>
         </is>
       </c>
-      <c r="J51" s="0" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K51" s="0" t="inlineStr">
+      <c r="L51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:198</t>
         </is>
@@ -2837,15 +3090,20 @@
       </c>
       <c r="I52" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Livello {major}</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {major}</t>
         </is>
       </c>
-      <c r="J52" s="0" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K52" s="0" t="inlineStr">
+      <c r="L52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:207, app.js:255</t>
         </is>
@@ -2889,15 +3147,20 @@
       </c>
       <c r="I53" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name} · Talismano {x}</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {x}</t>
         </is>
       </c>
-      <c r="J53" s="0" t="inlineStr">
+      <c r="K53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K53" s="0" t="inlineStr">
+      <c r="L53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:245</t>
         </is>
@@ -2941,15 +3204,20 @@
       </c>
       <c r="I54" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Livello {major}, fase {step} di {steps}</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {major}, {step}, {steps}</t>
         </is>
       </c>
-      <c r="J54" s="0" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K54" s="0" t="inlineStr">
+      <c r="L54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:255</t>
         </is>
@@ -2993,15 +3261,20 @@
       </c>
       <c r="I55" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sottolivelli del livello {major}</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {major}</t>
         </is>
       </c>
-      <c r="J55" s="0" t="inlineStr">
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K55" s="0" t="inlineStr">
+      <c r="L55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:255</t>
         </is>
@@ -3043,12 +3316,17 @@
           <t xml:space="preserve">Configura el nivel actual y el objetivo de cada uno de los 18 talismanes.</t>
         </is>
       </c>
-      <c r="J56" s="0" t="inlineStr">
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imposta il livello attuale e l’obiettivo di ciascuno dei 18 talismani.</t>
+        </is>
+      </c>
+      <c r="K56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K56" s="0" t="inlineStr">
+      <c r="L56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:74</t>
         </is>
@@ -3095,12 +3373,17 @@
           <t xml:space="preserve">Bajar objetivo</t>
         </is>
       </c>
-      <c r="J57" s="0" t="inlineStr">
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riduci obiettivo</t>
+        </is>
+      </c>
+      <c r="K57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K57" s="0" t="inlineStr">
+      <c r="L57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:100</t>
         </is>
@@ -3147,12 +3430,17 @@
           <t xml:space="preserve">Subir objetivo</t>
         </is>
       </c>
-      <c r="J58" s="0" t="inlineStr">
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aumenta obiettivo</t>
+        </is>
+      </c>
+      <c r="K58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K58" s="0" t="inlineStr">
+      <c r="L58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:100</t>
         </is>
@@ -3199,12 +3487,17 @@
           <t xml:space="preserve">Aplicar</t>
         </is>
       </c>
-      <c r="J59" s="0" t="inlineStr">
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applica</t>
+        </is>
+      </c>
+      <c r="K59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K59" s="0" t="inlineStr">
+      <c r="L59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:103</t>
         </is>
@@ -3246,12 +3539,17 @@
           <t xml:space="preserve">Investigación T11</t>
         </is>
       </c>
-      <c r="J60" s="0" t="inlineStr">
+      <c r="I60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ricerca T11</t>
+        </is>
+      </c>
+      <c r="K60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K60" s="0" t="inlineStr">
+      <c r="L60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:81</t>
         </is>
@@ -3293,12 +3591,17 @@
           <t xml:space="preserve">Elige tu tropa y toca una investigación para ajustar su nivel actual y su objetivo.</t>
         </is>
       </c>
-      <c r="J61" s="0" t="inlineStr">
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scegli la tua truppa, poi tocca una ricerca per impostarne il livello attuale e l’obiettivo.</t>
+        </is>
+      </c>
+      <c r="K61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K61" s="0" t="inlineStr">
+      <c r="L61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:81</t>
         </is>
@@ -3340,12 +3643,17 @@
           <t xml:space="preserve">Tropa</t>
         </is>
       </c>
-      <c r="J62" s="0" t="inlineStr">
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Truppa</t>
+        </is>
+      </c>
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K62" s="0" t="inlineStr">
+      <c r="L62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:82</t>
         </is>
@@ -3387,12 +3695,17 @@
           <t xml:space="preserve">Reiniciar</t>
         </is>
       </c>
-      <c r="J63" s="0" t="inlineStr">
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Azzera</t>
+        </is>
+      </c>
+      <c r="K63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K63" s="0" t="inlineStr">
+      <c r="L63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:88</t>
         </is>
@@ -3434,12 +3747,17 @@
           <t xml:space="preserve">Todo al máx.</t>
         </is>
       </c>
-      <c r="J64" s="0" t="inlineStr">
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tutto al max</t>
+        </is>
+      </c>
+      <c r="K64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K64" s="0" t="inlineStr">
+      <c r="L64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:88, t12.js:297</t>
         </is>
@@ -3481,12 +3799,17 @@
           <t xml:space="preserve">Ajusta el nivel actual de esta investigación y el nivel que quieres alcanzar.</t>
         </is>
       </c>
-      <c r="J65" s="0" t="inlineStr">
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imposta il livello attuale di questa ricerca e quello che vuoi raggiungere.</t>
+        </is>
+      </c>
+      <c r="K65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K65" s="0" t="inlineStr">
+      <c r="L65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:95</t>
         </is>
@@ -3533,12 +3856,17 @@
           <t xml:space="preserve">Bajar nivel actual</t>
         </is>
       </c>
-      <c r="J66" s="0" t="inlineStr">
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riduci livello attuale</t>
+        </is>
+      </c>
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K66" s="0" t="inlineStr">
+      <c r="L66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:98</t>
         </is>
@@ -3585,12 +3913,17 @@
           <t xml:space="preserve">Subir nivel actual</t>
         </is>
       </c>
-      <c r="J67" s="0" t="inlineStr">
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aumenta livello attuale</t>
+        </is>
+      </c>
+      <c r="K67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K67" s="0" t="inlineStr">
+      <c r="L67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:98</t>
         </is>
@@ -3639,15 +3972,20 @@
       </c>
       <c r="I68" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">, bloccata</t>
+        </is>
+      </c>
+      <c r="J68" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="J68" s="0" t="inlineStr">
+      <c r="K68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K68" s="0" t="inlineStr">
+      <c r="L68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:101, t12.js:210, t12.js:289</t>
         </is>
@@ -3696,15 +4034,20 @@
       </c>
       <c r="I69" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name}: livello {from} di {max}{x}{x}</t>
+        </is>
+      </c>
+      <c r="J69" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {from}, {max}, {x}</t>
         </is>
       </c>
-      <c r="J69" s="0" t="inlineStr">
+      <c r="K69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K69" s="0" t="inlineStr">
+      <c r="L69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:101, t12.js:210</t>
         </is>
@@ -3746,12 +4089,17 @@
           <t xml:space="preserve">Costo de investigación</t>
         </is>
       </c>
-      <c r="J70" s="0" t="inlineStr">
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costo della ricerca</t>
+        </is>
+      </c>
+      <c r="K70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K70" s="0" t="inlineStr">
+      <c r="L70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:133, t12.js:373</t>
         </is>
@@ -3800,15 +4148,20 @@
       </c>
       <c r="I71" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name}: livello {from} di 5{x}</t>
+        </is>
+      </c>
+      <c r="J71" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {from}, {x}</t>
         </is>
       </c>
-      <c r="J71" s="0" t="inlineStr">
+      <c r="K71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K71" s="0" t="inlineStr">
+      <c r="L71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:289</t>
         </is>
@@ -3847,15 +4200,20 @@
       </c>
       <c r="I72" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">obiettivo {to}</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau ajouté après « niveau … sur … »</t>
         </is>
       </c>
-      <c r="J72" s="0" t="inlineStr">
+      <c r="K72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K72" s="0" t="inlineStr">
+      <c r="L72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:101, t12.js:210</t>
         </is>
@@ -3899,15 +4257,20 @@
       </c>
       <c r="I73" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{name} Liv. {min}</t>
+        </is>
+      </c>
+      <c r="J73" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ligne de prérequis (précédée de ✓ ou ✗)</t>
         </is>
       </c>
-      <c r="J73" s="0" t="inlineStr">
+      <c r="K73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K73" s="0" t="inlineStr">
+      <c r="L73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:169, t12.js:406</t>
         </is>
@@ -3956,15 +4319,20 @@
       </c>
       <c r="I74" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REQUISITI{x}</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="J74" s="0" t="inlineStr">
+      <c r="K74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K74" s="0" t="inlineStr">
+      <c r="L74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:168, t12.js:405</t>
         </is>
@@ -4006,12 +4374,17 @@
           <t xml:space="preserve">Investigación T12</t>
         </is>
       </c>
-      <c r="J75" s="0" t="inlineStr">
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ricerca T12</t>
+        </is>
+      </c>
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K75" s="0" t="inlineStr">
+      <c r="L75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:109</t>
         </is>
@@ -4053,12 +4426,17 @@
           <t xml:space="preserve">Elige tu tropa, desbloquea la unidad sublime y luego haz progresar su árbol.</t>
         </is>
       </c>
-      <c r="J76" s="0" t="inlineStr">
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scegli la tua truppa, sblocca l’unità esaltata e poi fai progredire il suo albero.</t>
+        </is>
+      </c>
+      <c r="K76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K76" s="0" t="inlineStr">
+      <c r="L76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:109</t>
         </is>
@@ -4100,12 +4478,17 @@
           <t xml:space="preserve">Sección</t>
         </is>
       </c>
-      <c r="J77" s="0" t="inlineStr">
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sezione</t>
+        </is>
+      </c>
+      <c r="K77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K77" s="0" t="inlineStr">
+      <c r="L77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:115</t>
         </is>
@@ -4152,12 +4535,17 @@
           <t xml:space="preserve">Desbloqueo</t>
         </is>
       </c>
-      <c r="J78" s="0" t="inlineStr">
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sblocco</t>
+        </is>
+      </c>
+      <c r="K78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K78" s="0" t="inlineStr">
+      <c r="L78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:116</t>
         </is>
@@ -4204,12 +4592,17 @@
           <t xml:space="preserve">Árbol</t>
         </is>
       </c>
-      <c r="J79" s="0" t="inlineStr">
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Albero</t>
+        </is>
+      </c>
+      <c r="K79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K79" s="0" t="inlineStr">
+      <c r="L79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:117</t>
         </is>
@@ -4251,12 +4644,17 @@
           <t xml:space="preserve">Unidad aún no desbloqueada: puedes ajustar el árbol para planificar.</t>
         </is>
       </c>
-      <c r="J80" s="0" t="inlineStr">
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unità non ancora sbloccata: puoi comunque impostare l’albero per pianificare.</t>
+        </is>
+      </c>
+      <c r="K80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K80" s="0" t="inlineStr">
+      <c r="L80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:119</t>
         </is>
@@ -4303,12 +4701,17 @@
           <t xml:space="preserve">Menos 10</t>
         </is>
       </c>
-      <c r="J81" s="0" t="inlineStr">
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meno 10</t>
+        </is>
+      </c>
+      <c r="K81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K81" s="0" t="inlineStr">
+      <c r="L81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:132</t>
         </is>
@@ -4355,12 +4758,17 @@
           <t xml:space="preserve">Más 10</t>
         </is>
       </c>
-      <c r="J82" s="0" t="inlineStr">
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Più 10</t>
+        </is>
+      </c>
+      <c r="K82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K82" s="0" t="inlineStr">
+      <c r="L82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:132</t>
         </is>
@@ -4404,15 +4812,20 @@
       </c>
       <c r="I83" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">sbloccata</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="J83" s="0" t="inlineStr">
+      <c r="K83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K83" s="0" t="inlineStr">
+      <c r="L83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:207</t>
         </is>
@@ -4456,15 +4869,20 @@
       </c>
       <c r="I84" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">non ancora sbloccata</t>
+        </is>
+      </c>
+      <c r="J84" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="J84" s="0" t="inlineStr">
+      <c r="K84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K84" s="0" t="inlineStr">
+      <c r="L84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:207</t>
         </is>
@@ -4513,15 +4931,20 @@
       </c>
       <c r="I85" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">della Fanteria</t>
+        </is>
+      </c>
+      <c r="J85" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Morceau de phrase : sera regroupé avec son contexte lors du branchement</t>
         </is>
       </c>
-      <c r="J85" s="0" t="inlineStr">
+      <c r="K85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K85" s="0" t="inlineStr">
+      <c r="L85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:293</t>
         </is>
@@ -4570,15 +4993,20 @@
       </c>
       <c r="I86" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{label}: meno 1</t>
+        </is>
+      </c>
+      <c r="J86" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {label}</t>
         </is>
       </c>
-      <c r="J86" s="0" t="inlineStr">
+      <c r="K86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K86" s="0" t="inlineStr">
+      <c r="L86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:297</t>
         </is>
@@ -4627,15 +5055,20 @@
       </c>
       <c r="I87" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{label}: più 1</t>
+        </is>
+      </c>
+      <c r="J87" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {label}</t>
         </is>
       </c>
-      <c r="J87" s="0" t="inlineStr">
+      <c r="K87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K87" s="0" t="inlineStr">
+      <c r="L87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:297</t>
         </is>
@@ -4684,15 +5117,20 @@
       </c>
       <c r="I88" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{label}: livello max</t>
+        </is>
+      </c>
+      <c r="J88" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {label}</t>
         </is>
       </c>
-      <c r="J88" s="0" t="inlineStr">
+      <c r="K88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K88" s="0" t="inlineStr">
+      <c r="L88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:297</t>
         </is>
@@ -4734,12 +5172,17 @@
           <t xml:space="preserve">Costo total del desbloqueo</t>
         </is>
       </c>
-      <c r="J89" s="0" t="inlineStr">
+      <c r="I89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costo totale dello sblocco</t>
+        </is>
+      </c>
+      <c r="K89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K89" s="0" t="inlineStr">
+      <c r="L89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:373</t>
         </is>
@@ -4783,15 +5226,20 @@
       </c>
       <c r="I90" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{x} sbloccata</t>
+        </is>
+      </c>
+      <c r="J90" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="J90" s="0" t="inlineStr">
+      <c r="K90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K90" s="0" t="inlineStr">
+      <c r="L90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:406</t>
         </is>
@@ -4833,12 +5281,17 @@
           <t xml:space="preserve">{done}/5 piezas</t>
         </is>
       </c>
-      <c r="J91" s="0" t="inlineStr">
+      <c r="I91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{done}/5 pezzi</t>
+        </is>
+      </c>
+      <c r="K91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Oui</t>
         </is>
       </c>
-      <c r="K91" s="0" t="inlineStr">
+      <c r="L91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:300</t>
         </is>
@@ -4877,15 +5330,20 @@
       </c>
       <c r="I92" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">FINO AL LIVELLO {to}</t>
+        </is>
+      </c>
+      <c r="J92" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {to}</t>
         </is>
       </c>
-      <c r="J92" s="0" t="inlineStr">
+      <c r="K92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K92" s="0" t="inlineStr">
+      <c r="L92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:168, t12.js:405</t>
         </is>
@@ -4924,15 +5382,20 @@
       </c>
       <c r="I93" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">del {x}</t>
+        </is>
+      </c>
+      <c r="J93" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="J93" s="0" t="inlineStr">
+      <c r="K93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K93" s="0" t="inlineStr">
+      <c r="L93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:293</t>
         </is>
@@ -4969,12 +5432,17 @@
           <t xml:space="preserve">El árbol de investigación está disponible</t>
         </is>
       </c>
-      <c r="J94" s="0" t="inlineStr">
+      <c r="I94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’albero di ricerca è disponibile</t>
+        </is>
+      </c>
+      <c r="K94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K94" s="0" t="inlineStr">
+      <c r="L94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:302</t>
         </is>
@@ -5011,12 +5479,17 @@
           <t xml:space="preserve">Indica solo el estado actual de tu Gobernador.</t>
         </is>
       </c>
-      <c r="J95" s="0" t="inlineStr">
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inserisci solo lo stato attuale del tuo Capo.</t>
+        </is>
+      </c>
+      <c r="K95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K95" s="0" t="inlineStr">
+      <c r="L95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:142</t>
         </is>
@@ -5055,15 +5528,20 @@
       </c>
       <c r="I96" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">EQUIPAGGIAMENTO ATTUALE</t>
+        </is>
+      </c>
+      <c r="J96" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J96" s="0" t="inlineStr">
+      <c r="K96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K96" s="0" t="inlineStr">
+      <c r="L96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:142</t>
         </is>
@@ -5100,12 +5578,17 @@
           <t xml:space="preserve">Elegir un nivel</t>
         </is>
       </c>
-      <c r="J97" s="0" t="inlineStr">
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scegli un livello</t>
+        </is>
+      </c>
+      <c r="K97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K97" s="0" t="inlineStr">
+      <c r="L97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:143</t>
         </is>
@@ -5142,12 +5625,17 @@
           <t xml:space="preserve">Calefactor objetivo</t>
         </is>
       </c>
-      <c r="J98" s="0" t="inlineStr">
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fornace obiettivo</t>
+        </is>
+      </c>
+      <c r="K98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K98" s="0" t="inlineStr">
+      <c r="L98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:114</t>
         </is>
@@ -5186,15 +5674,20 @@
       </c>
       <c r="I99" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Apri {name}, livello attuale {x}</t>
+        </is>
+      </c>
+      <c r="J99" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {name}, {x}</t>
         </is>
       </c>
-      <c r="J99" s="0" t="inlineStr">
+      <c r="K99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K99" s="0" t="inlineStr">
+      <c r="L99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:151</t>
         </is>
@@ -5231,12 +5724,17 @@
           <t xml:space="preserve">⚙️ Aleación</t>
         </is>
       </c>
-      <c r="J100" s="0" t="inlineStr">
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚙️ Lega</t>
+        </is>
+      </c>
+      <c r="K100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K100" s="0" t="inlineStr">
+      <c r="L100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -5273,12 +5771,17 @@
           <t xml:space="preserve">✨ Pulidora</t>
         </is>
       </c>
-      <c r="J101" s="0" t="inlineStr">
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✨ Lucidatura</t>
+        </is>
+      </c>
+      <c r="K101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K101" s="0" t="inlineStr">
+      <c r="L101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -5315,12 +5818,17 @@
           <t xml:space="preserve">📜 Planos</t>
         </is>
       </c>
-      <c r="J102" s="0" t="inlineStr">
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📜 Progetti</t>
+        </is>
+      </c>
+      <c r="K102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K102" s="0" t="inlineStr">
+      <c r="L102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -5357,12 +5865,17 @@
           <t xml:space="preserve">🟠 Ámbar lunar</t>
         </is>
       </c>
-      <c r="J103" s="0" t="inlineStr">
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🟠 Ambra lunare</t>
+        </is>
+      </c>
+      <c r="K103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K103" s="0" t="inlineStr">
+      <c r="L103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -5401,15 +5914,20 @@
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">COSTO EQUIPAGGIAMENTO</t>
+        </is>
+      </c>
+      <c r="J104" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J104" s="0" t="inlineStr">
+      <c r="K104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K104" s="0" t="inlineStr">
+      <c r="L104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -5446,12 +5964,17 @@
           <t xml:space="preserve">Objetivos de las 6 piezas</t>
         </is>
       </c>
-      <c r="J105" s="0" t="inlineStr">
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obiettivi dei 6 pezzi</t>
+        </is>
+      </c>
+      <c r="K105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K105" s="0" t="inlineStr">
+      <c r="L105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -5490,15 +6013,20 @@
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">COSTO TALISMANI</t>
+        </is>
+      </c>
+      <c r="J106" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J106" s="0" t="inlineStr">
+      <c r="K106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K106" s="0" t="inlineStr">
+      <c r="L106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152, app.js:155</t>
         </is>
@@ -5535,12 +6063,17 @@
           <t xml:space="preserve">Objetivos de los 18 talismanes</t>
         </is>
       </c>
-      <c r="J107" s="0" t="inlineStr">
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obiettivi dei 18 talismani</t>
+        </is>
+      </c>
+      <c r="K107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K107" s="0" t="inlineStr">
+      <c r="L107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152</t>
         </is>
@@ -5577,12 +6110,17 @@
           <t xml:space="preserve">📘 Guías</t>
         </is>
       </c>
-      <c r="J108" s="0" t="inlineStr">
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📘 Guide</t>
+        </is>
+      </c>
+      <c r="K108" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K108" s="0" t="inlineStr">
+      <c r="L108" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152, app.js:155</t>
         </is>
@@ -5619,12 +6157,17 @@
           <t xml:space="preserve">💠 Planos</t>
         </is>
       </c>
-      <c r="J109" s="0" t="inlineStr">
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💠 Progetti</t>
+        </is>
+      </c>
+      <c r="K109" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K109" s="0" t="inlineStr">
+      <c r="L109" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:152, app.js:155</t>
         </is>
@@ -5663,15 +6206,20 @@
       </c>
       <c r="I110" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">LIVELLO ATTUALE</t>
+        </is>
+      </c>
+      <c r="J110" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Affiché en MAJUSCULES</t>
         </is>
       </c>
-      <c r="J110" s="0" t="inlineStr">
+      <c r="K110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K110" s="0" t="inlineStr">
+      <c r="L110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153, app.js:154, app.js:172, app.js:244</t>
         </is>
@@ -5708,12 +6256,17 @@
           <t xml:space="preserve">Configura cada par directamente</t>
         </is>
       </c>
-      <c r="J111" s="0" t="inlineStr">
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imposta direttamente ogni coppia</t>
+        </is>
+      </c>
+      <c r="K111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K111" s="0" t="inlineStr">
+      <c r="L111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153</t>
         </is>
@@ -5750,12 +6303,17 @@
           <t xml:space="preserve">actual › objetivo</t>
         </is>
       </c>
-      <c r="J112" s="0" t="inlineStr">
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attuale › obiettivo</t>
+        </is>
+      </c>
+      <c r="K112" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K112" s="0" t="inlineStr">
+      <c r="L112" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:153</t>
         </is>
@@ -5794,15 +6352,20 @@
       </c>
       <c r="I113" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Talismano {x}</t>
+        </is>
+      </c>
+      <c r="J113" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="J113" s="0" t="inlineStr">
+      <c r="K113" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K113" s="0" t="inlineStr">
+      <c r="L113" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:154, app.js:156, app.js:172</t>
         </is>
@@ -5839,12 +6402,17 @@
           <t xml:space="preserve">Recursos necesarios</t>
         </is>
       </c>
-      <c r="J114" s="0" t="inlineStr">
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Risorse necessarie</t>
+        </is>
+      </c>
+      <c r="K114" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K114" s="0" t="inlineStr">
+      <c r="L114" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -5883,15 +6451,20 @@
       </c>
       <c r="I115" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sottolivello {step} di {x}</t>
+        </is>
+      </c>
+      <c r="J115" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {step}, {x}</t>
         </is>
       </c>
-      <c r="J115" s="0" t="inlineStr">
+      <c r="K115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K115" s="0" t="inlineStr">
+      <c r="L115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:197</t>
         </is>
@@ -5928,19 +6501,24 @@
           <t xml:space="preserve">Elegir el subnivel</t>
         </is>
       </c>
-      <c r="J116" s="0" t="inlineStr">
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scegli il sottolivello</t>
+        </is>
+      </c>
+      <c r="K116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non (situation rare ou ancien texte)</t>
         </is>
       </c>
-      <c r="K116" s="0" t="inlineStr">
+      <c r="L116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:310</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K116"/>
+  <autoFilter ref="A3:L116"/>
 </worksheet>
 </file>
 
@@ -5954,9 +6532,11 @@
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6011,15 +6591,25 @@
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiabilité IT</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Remarques</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pages où il apparaît</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
@@ -6061,12 +6651,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fornace</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Accueil, Chaudière, Menu</t>
         </is>
       </c>
-      <c r="J4" s="0" t="inlineStr">
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:8</t>
         </is>
@@ -6108,12 +6708,22 @@
           <t xml:space="preserve">Nom générique (traduction de Bague)</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anello</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction du nom choisi pour le site)</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -6157,15 +6767,25 @@
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bastone</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction du nom choisi pour le site)</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nouveau nom FR (aujourd’hui « Canne » sur le site, changera au branchement)</t>
         </is>
       </c>
-      <c r="I6" s="0" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="J6" s="0" t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -6207,12 +6827,22 @@
           <t xml:space="preserve">Nom générique (traduction de Casque)</t>
         </is>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elmo</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction du nom choisi pour le site)</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans, Équipement</t>
         </is>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="L7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -6256,15 +6886,25 @@
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Cappotto</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction du nom choisi pour le site)</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nouveau nom FR (aujourd’hui « Veste » sur le site, changera au branchement)</t>
         </is>
       </c>
-      <c r="I8" s="0" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="L8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -6306,12 +6946,22 @@
           <t xml:space="preserve">Nom générique (traduction de Montre)</t>
         </is>
       </c>
-      <c r="I9" s="0" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orologio</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction du nom choisi pour le site)</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="L9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -6353,12 +7003,22 @@
           <t xml:space="preserve">Nom générique (traduction de Pantalon)</t>
         </is>
       </c>
-      <c r="I10" s="0" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pantaloni</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom générique (traduction du nom choisi pour le site)</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="L10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:8</t>
         </is>
@@ -6402,15 +7062,25 @@
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Leggendario{x}</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="J11" s="0" t="inlineStr">
+      <c r="L11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:9</t>
         </is>
@@ -6452,12 +7122,22 @@
           <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
-      <c r="I12" s="0" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mitico</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="L12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:4, data.js:131</t>
         </is>
@@ -6501,15 +7181,25 @@
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mitico{x}</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I13" s="0" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="L13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:7</t>
         </is>
@@ -6553,15 +7243,25 @@
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Non comune{x}</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I14" s="0" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="J14" s="0" t="inlineStr">
+      <c r="L14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:3</t>
         </is>
@@ -6605,15 +7305,25 @@
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Raro{x}</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I15" s="0" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="J15" s="0" t="inlineStr">
+      <c r="L15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:4</t>
         </is>
@@ -6655,12 +7365,22 @@
           <t xml:space="preserve">Validé par toi</t>
         </is>
       </c>
-      <c r="I16" s="0" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epico</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="J16" s="0" t="inlineStr">
+      <c r="L16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:4, data.js:123</t>
         </is>
@@ -6704,15 +7424,25 @@
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Epico{x}</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {x}</t>
         </is>
       </c>
-      <c r="I17" s="0" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="J17" s="0" t="inlineStr">
+      <c r="L17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:5</t>
         </is>
@@ -6754,12 +7484,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I18" s="0" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armamento esaltato</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J18" s="0" t="inlineStr">
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -6801,12 +7541,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placcatura fusa</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J19" s="0" t="inlineStr">
+      <c r="L19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:27</t>
         </is>
@@ -6848,12 +7598,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armatura Ardente</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J20" s="0" t="inlineStr">
+      <c r="L20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:49</t>
         </is>
@@ -6895,12 +7655,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I21" s="0" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armatura di Cristallo</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J21" s="0" t="inlineStr">
+      <c r="L21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:50</t>
         </is>
@@ -6942,12 +7712,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I22" s="0" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sentiero di guerra esaltato</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="L22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -6989,12 +7769,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I23" s="0" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scudo di Fiamme</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J23" s="0" t="inlineStr">
+      <c r="L23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:48</t>
         </is>
@@ -7036,12 +7826,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I24" s="0" t="inlineStr">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scudi fusi</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J24" s="0" t="inlineStr">
+      <c r="L24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:27</t>
         </is>
@@ -7083,12 +7883,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I25" s="0" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cadenza esaltata</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J25" s="0" t="inlineStr">
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -7130,12 +7940,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I26" s="0" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elmo esaltato</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J26" s="0" t="inlineStr">
+      <c r="L26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -7177,12 +7997,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I27" s="0" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elmi fusi</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J27" s="0" t="inlineStr">
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:28</t>
         </is>
@@ -7224,12 +8054,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I28" s="0" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carica Ardente</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J28" s="0" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:49</t>
         </is>
@@ -7271,12 +8111,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I29" s="0" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corazza a piastre esaltata</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J29" s="0" t="inlineStr">
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -7318,12 +8168,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I30" s="0" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corona di guerra esaltata</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J30" s="0" t="inlineStr">
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -7365,12 +8225,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I31" s="0" t="inlineStr">
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supremazia solare</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J31" s="0" t="inlineStr">
+      <c r="L31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:37</t>
         </is>
@@ -7412,12 +8282,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I32" s="0" t="inlineStr">
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Addestramento della Fanteria esaltata</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J32" s="0" t="inlineStr">
+      <c r="L32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:35</t>
         </is>
@@ -7459,12 +8339,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I33" s="0" t="inlineStr">
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Addestramento dei Lancieri esaltati</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J33" s="0" t="inlineStr">
+      <c r="L33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:35</t>
         </is>
@@ -7506,12 +8396,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I34" s="0" t="inlineStr">
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Addestramento dei Tiratori esaltati</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J34" s="0" t="inlineStr">
+      <c r="L34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:35</t>
         </is>
@@ -7555,15 +8455,25 @@
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Addestramento di {unit} Helios</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
         </is>
       </c>
-      <c r="I35" s="0" t="inlineStr">
+      <c r="K35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J35" s="0" t="inlineStr">
+      <c r="L35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:61</t>
         </is>
@@ -7607,15 +8517,25 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Addestramento di Fanteria Helios</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Forme élidée produite par le code pour l’infanterie</t>
         </is>
       </c>
-      <c r="I36" s="0" t="inlineStr">
+      <c r="K36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J36" s="0" t="inlineStr">
+      <c r="L36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:61</t>
         </is>
@@ -7657,12 +8577,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I37" s="0" t="inlineStr">
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Squadra di Fiamme</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J37" s="0" t="inlineStr">
+      <c r="L37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:53</t>
         </is>
@@ -7704,12 +8634,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I38" s="0" t="inlineStr">
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traversata esaltata</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J38" s="0" t="inlineStr">
+      <c r="L38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -7751,12 +8691,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I39" s="0" t="inlineStr">
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freccia di Cristallo</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J39" s="0" t="inlineStr">
+      <c r="L39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:50</t>
         </is>
@@ -7798,12 +8748,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I40" s="0" t="inlineStr">
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colpo di Fiamme</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J40" s="0" t="inlineStr">
+      <c r="L40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:48</t>
         </is>
@@ -7845,12 +8805,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I41" s="0" t="inlineStr">
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impugnatura fusa</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J41" s="0" t="inlineStr">
+      <c r="L41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:29</t>
         </is>
@@ -7892,12 +8862,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I42" s="0" t="inlineStr">
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guardia fusa</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J42" s="0" t="inlineStr">
+      <c r="L42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:27</t>
         </is>
@@ -7939,12 +8919,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I43" s="0" t="inlineStr">
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spallaccio esaltato</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J43" s="0" t="inlineStr">
+      <c r="L43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -7986,12 +8976,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I44" s="0" t="inlineStr">
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guardiano Ardente</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J44" s="0" t="inlineStr">
+      <c r="L44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:49</t>
         </is>
@@ -8033,12 +9033,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I45" s="0" t="inlineStr">
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lame fuse</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J45" s="0" t="inlineStr">
+      <c r="L45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:27</t>
         </is>
@@ -8080,12 +9090,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I46" s="0" t="inlineStr">
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancia fusa</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J46" s="0" t="inlineStr">
+      <c r="L46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:28</t>
         </is>
@@ -8127,12 +9147,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I47" s="0" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancia Ardente</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J47" s="0" t="inlineStr">
+      <c r="L47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:49</t>
         </is>
@@ -8174,12 +9204,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I48" s="0" t="inlineStr">
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legione di Fiamme</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J48" s="0" t="inlineStr">
+      <c r="L48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:56</t>
         </is>
@@ -8221,12 +9261,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I49" s="0" t="inlineStr">
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantello esaltato</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J49" s="0" t="inlineStr">
+      <c r="L49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -8268,12 +9318,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I50" s="0" t="inlineStr">
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muro indomabile</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J50" s="0" t="inlineStr">
+      <c r="L50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:31</t>
         </is>
@@ -8315,12 +9375,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I51" s="0" t="inlineStr">
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falange meridiana</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J51" s="0" t="inlineStr">
+      <c r="L51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:31</t>
         </is>
@@ -8362,12 +9432,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I52" s="0" t="inlineStr">
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Picca esaltata</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J52" s="0" t="inlineStr">
+      <c r="L52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -8409,12 +9489,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I53" s="0" t="inlineStr">
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bastione esaltato</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J53" s="0" t="inlineStr">
+      <c r="L53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:15</t>
         </is>
@@ -8456,12 +9546,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I54" s="0" t="inlineStr">
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primo soccorso della Fanteria esaltata</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J54" s="0" t="inlineStr">
+      <c r="L54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:34</t>
         </is>
@@ -8503,12 +9603,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I55" s="0" t="inlineStr">
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primo soccorso dei Lancieri esaltati</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J55" s="0" t="inlineStr">
+      <c r="L55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:34</t>
         </is>
@@ -8550,12 +9660,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I56" s="0" t="inlineStr">
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primo soccorso dei Tiratori esaltati</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J56" s="0" t="inlineStr">
+      <c r="L56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:34</t>
         </is>
@@ -8597,12 +9717,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I57" s="0" t="inlineStr">
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protezione di Cristallo</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J57" s="0" t="inlineStr">
+      <c r="L57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:50</t>
         </is>
@@ -8644,12 +9774,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I58" s="0" t="inlineStr">
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protezione di Fiamme</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J58" s="0" t="inlineStr">
+      <c r="L58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:48</t>
         </is>
@@ -8691,12 +9831,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I59" s="0" t="inlineStr">
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bracciale fuso</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J59" s="0" t="inlineStr">
+      <c r="L59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:28</t>
         </is>
@@ -8738,12 +9888,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I60" s="0" t="inlineStr">
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiro di precisione fuso</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J60" s="0" t="inlineStr">
+      <c r="L60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:29</t>
         </is>
@@ -8785,12 +9945,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
-      <c r="I61" s="0" t="inlineStr">
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cura della Fanteria esaltata</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J61" s="0" t="inlineStr">
+      <c r="L61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:33</t>
         </is>
@@ -8832,12 +10002,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I62" s="0" t="inlineStr">
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cura dei Lancieri esaltati</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J62" s="0" t="inlineStr">
+      <c r="L62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:33</t>
         </is>
@@ -8879,12 +10059,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I63" s="0" t="inlineStr">
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cura dei Tiratori esaltati</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J63" s="0" t="inlineStr">
+      <c r="L63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:33</t>
         </is>
@@ -8926,12 +10116,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I64" s="0" t="inlineStr">
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tattiche fuse</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J64" s="0" t="inlineStr">
+      <c r="L64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:28</t>
         </is>
@@ -8973,12 +10173,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I65" s="0" t="inlineStr">
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tenuta da guerra esaltata</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J65" s="0" t="inlineStr">
+      <c r="L65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -9020,12 +10230,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I66" s="0" t="inlineStr">
+      <c r="H66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuoco stellare</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J66" s="0" t="inlineStr">
+      <c r="L66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:31</t>
         </is>
@@ -9067,12 +10287,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I67" s="0" t="inlineStr">
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colpo fuso</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J67" s="0" t="inlineStr">
+      <c r="L67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:29</t>
         </is>
@@ -9114,12 +10344,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I68" s="0" t="inlineStr">
+      <c r="H68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tomahawk di Fiamme</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J68" s="0" t="inlineStr">
+      <c r="L68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:48</t>
         </is>
@@ -9161,12 +10401,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I69" s="0" t="inlineStr">
+      <c r="H69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trombone esaltato</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J69" s="0" t="inlineStr">
+      <c r="L69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -9208,12 +10458,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I70" s="0" t="inlineStr">
+      <c r="H70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visione di Cristallo</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J70" s="0" t="inlineStr">
+      <c r="L70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:50</t>
         </is>
@@ -9255,12 +10515,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I71" s="0" t="inlineStr">
+      <c r="H71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Velo esaltato</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J71" s="0" t="inlineStr">
+      <c r="L71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:17</t>
         </is>
@@ -9304,15 +10574,25 @@
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">{unit} Helios</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
         </is>
       </c>
-      <c r="I72" s="0" t="inlineStr">
+      <c r="K72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J72" s="0" t="inlineStr">
+      <c r="L72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:59</t>
         </is>
@@ -9356,15 +10636,25 @@
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Primo Soccorso di {unit} Helios</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J73" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
         </is>
       </c>
-      <c r="I73" s="0" t="inlineStr">
+      <c r="K73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J73" s="0" t="inlineStr">
+      <c r="L73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:62</t>
         </is>
@@ -9408,15 +10698,25 @@
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Cura di {unit} Helios</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
         </is>
       </c>
-      <c r="I74" s="0" t="inlineStr">
+      <c r="K74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
         </is>
       </c>
-      <c r="J74" s="0" t="inlineStr">
+      <c r="L74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:60</t>
         </is>
@@ -9458,12 +10758,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I75" s="0" t="inlineStr">
+      <c r="H75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scaglie fuse</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J75" s="0" t="inlineStr">
+      <c r="L75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:29</t>
         </is>
@@ -9505,12 +10815,22 @@
           <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
-      <c r="I76" s="0" t="inlineStr">
+      <c r="H76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spalliera esaltata</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J76" s="0" t="inlineStr">
+      <c r="L76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:16</t>
         </is>
@@ -9552,12 +10872,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I77" s="0" t="inlineStr">
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceleratori</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
-      <c r="J77" s="0" t="inlineStr">
+      <c r="L77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t11.js:131, t12.js:370</t>
         </is>
@@ -9599,12 +10929,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I78" s="0" t="inlineStr">
+      <c r="H78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acciaio</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="J78" s="0" t="inlineStr">
+      <c r="L78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:126, t12.js:353, t12.js:365</t>
         </is>
@@ -9646,12 +10986,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I79" s="0" t="inlineStr">
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lega temprata</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="J79" s="0" t="inlineStr">
+      <c r="L79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -9693,12 +11043,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I80" s="0" t="inlineStr">
+      <c r="H80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ambra lunare</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="J80" s="0" t="inlineStr">
+      <c r="L80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -9740,12 +11100,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I81" s="0" t="inlineStr">
+      <c r="H81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legno</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
-      <c r="J81" s="0" t="inlineStr">
+      <c r="L81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t11.js:128, t12.js:367</t>
         </is>
@@ -9787,12 +11157,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I82" s="0" t="inlineStr">
+      <c r="H82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carbone</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
-      <c r="J82" s="0" t="inlineStr">
+      <c r="L82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t11.js:129, t12.js:368</t>
         </is>
@@ -9834,12 +11214,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I83" s="0" t="inlineStr">
+      <c r="H83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristallo di Fuoco</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière</t>
         </is>
       </c>
-      <c r="J83" s="0" t="inlineStr">
+      <c r="L83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149</t>
         </is>
@@ -9881,12 +11271,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I84" s="0" t="inlineStr">
+      <c r="H84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristallo di Fuoco raffinato</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T12</t>
         </is>
       </c>
-      <c r="J84" s="0" t="inlineStr">
+      <c r="L84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t12.js:352, t12.js:364</t>
         </is>
@@ -9928,12 +11328,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I85" s="0" t="inlineStr">
+      <c r="H85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ferro</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
-      <c r="J85" s="0" t="inlineStr">
+      <c r="L85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149, t11.js:130, t12.js:369</t>
         </is>
@@ -9975,12 +11385,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I86" s="0" t="inlineStr">
+      <c r="H86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frammento di Cristallo di Fuoco</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="J86" s="0" t="inlineStr">
+      <c r="L86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:125, t12.js:351, t12.js:363</t>
         </is>
@@ -10022,12 +11442,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I87" s="0" t="inlineStr">
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guida al talismano</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="J87" s="0" t="inlineStr">
+      <c r="L87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:223</t>
         </is>
@@ -10069,12 +11499,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I88" s="0" t="inlineStr">
+      <c r="H88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carne</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Chaudière</t>
         </is>
       </c>
-      <c r="J88" s="0" t="inlineStr">
+      <c r="L88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:149</t>
         </is>
@@ -10116,12 +11556,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I89" s="0" t="inlineStr">
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progetti di design</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="J89" s="0" t="inlineStr">
+      <c r="L89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -10163,12 +11613,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I90" s="0" t="inlineStr">
+      <c r="H90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progetto del talismano</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="J90" s="0" t="inlineStr">
+      <c r="L90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:224</t>
         </is>
@@ -10210,12 +11670,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I91" s="0" t="inlineStr">
+      <c r="H91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Segreti del talismano</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Talismans</t>
         </is>
       </c>
-      <c r="J91" s="0" t="inlineStr">
+      <c r="L91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:225</t>
         </is>
@@ -10257,12 +11727,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I92" s="0" t="inlineStr">
+      <c r="H92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soluzione lucidante</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Équipement</t>
         </is>
       </c>
-      <c r="J92" s="0" t="inlineStr">
+      <c r="L92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">app.js:155</t>
         </is>
@@ -10304,12 +11784,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I93" s="0" t="inlineStr">
+      <c r="H93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carne</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="J93" s="0" t="inlineStr">
+      <c r="L93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t11.js:127, t12.js:366</t>
         </is>
@@ -10351,12 +11841,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I94" s="0" t="inlineStr">
+      <c r="H94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attacco</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="J94" s="0" t="inlineStr">
+      <c r="L94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -10398,12 +11898,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I95" s="0" t="inlineStr">
+      <c r="H95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacità di schieramento</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J95" s="0" t="inlineStr">
+      <c r="L95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -10445,12 +11955,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I96" s="0" t="inlineStr">
+      <c r="H96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacità di schieramento</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J96" s="0" t="inlineStr">
+      <c r="L96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:293</t>
         </is>
@@ -10492,12 +12012,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I97" s="0" t="inlineStr">
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Difesa</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="J97" s="0" t="inlineStr">
+      <c r="L97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -10539,12 +12069,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I98" s="0" t="inlineStr">
+      <c r="H98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Letalità</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="J98" s="0" t="inlineStr">
+      <c r="L98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -10586,12 +12126,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I99" s="0" t="inlineStr">
+      <c r="H99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Potenza</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J99" s="0" t="inlineStr">
+      <c r="L99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">t12.js:309</t>
         </is>
@@ -10633,12 +12183,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I100" s="0" t="inlineStr">
+      <c r="H100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salute</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
-      <c r="J100" s="0" t="inlineStr">
+      <c r="L100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:24</t>
         </is>
@@ -10680,12 +12240,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I101" s="0" t="inlineStr">
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fanteria</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="J101" s="0" t="inlineStr">
+      <c r="L101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:83, app.js:151, app.js:152, app.js:153, app.js:199, app.js:204, app.js:206, data.js:8, data.js:46, t12.js:220</t>
         </is>
@@ -10727,12 +12297,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I102" s="0" t="inlineStr">
+      <c r="H102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fanteria esaltata</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J102" s="0" t="inlineStr">
+      <c r="L102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:12</t>
         </is>
@@ -10774,12 +12354,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I103" s="0" t="inlineStr">
+      <c r="H103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lanciere</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12, Talismans</t>
         </is>
       </c>
-      <c r="J103" s="0" t="inlineStr">
+      <c r="L103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:84, app.js:151, app.js:152, app.js:153, app.js:199, app.js:204, app.js:206, data.js:8, data.js:46, t12.js:220</t>
         </is>
@@ -10821,12 +12411,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I104" s="0" t="inlineStr">
+      <c r="H104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lanciere esaltato</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J104" s="0" t="inlineStr">
+      <c r="L104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:12</t>
         </is>
@@ -10868,12 +12468,22 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I105" s="0" t="inlineStr">
+      <c r="H105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiratore</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
-      <c r="J105" s="0" t="inlineStr">
+      <c r="L105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">index.html:85, data.js:8, data.js:46, t12.js:220</t>
         </is>
@@ -10915,19 +12525,29 @@
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="I106" s="0" t="inlineStr">
+      <c r="H106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiratore esaltato</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+        </is>
+      </c>
+      <c r="K106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="J106" s="0" t="inlineStr">
+      <c r="L106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J106"/>
+  <autoFilter ref="A3:L106"/>
 </worksheet>
 </file>
 

--- a/i18n/lexique.xlsx
+++ b/i18n/lexique.xlsx
@@ -10,7 +10,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textes interface'!$A$3:$L$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termes du jeu'!$A$3:$L$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termes du jeu'!$A$3:$L$117</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -147,7 +147,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   IT : textes d’interface traduits ; termes du jeu tous en proposition (jaune), faute de captures du jeu en italien.</t>
+          <t xml:space="preserve">   IT : termes du jeu relevés sur tes captures en italien (IMG_1358 à 1433), sauf les 15 pièces de déblocage T12, déduites (jaune).</t>
         </is>
       </c>
     </row>
@@ -218,7 +218,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termes du jeu : 103 noms (ressources, troupes, pièces, raretés, recherches T11/T12, statistiques).</t>
+          <t xml:space="preserve">Termes du jeu : 114 noms (ressources, troupes, pièces, raretés, recherches T11/T12, statistiques).</t>
         </is>
       </c>
     </row>
@@ -6656,9 +6656,9 @@
           <t xml:space="preserve">Fornace</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placcatura fusa</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Piastre fuse</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K19" s="0" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armatura Ardente</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Armatura ardente</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armatura di Cristallo</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Armatura di cristallo</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scudo di Fiamme</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Scudo fiamma</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
@@ -7831,9 +7831,9 @@
           <t xml:space="preserve">Scudi fusi</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K25" s="0" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
@@ -8002,9 +8002,9 @@
           <t xml:space="preserve">Elmi fusi</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K27" s="0" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carica Ardente</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Carica ardente</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K28" s="0" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K30" s="0" t="inlineStr">
@@ -8230,9 +8230,9 @@
           <t xml:space="preserve">Supremazia solare</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K31" s="0" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addestramento della Fanteria esaltata</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Addestramento fanteria esaltata</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.entrainement_lanciers_glorifies</t>
+          <t xml:space="preserve">game.entrainement_de_lancier_helios</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
@@ -8316,54 +8316,59 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entraînement de lanciers glorifiés</t>
+          <t xml:space="preserve">Entraînement de Lancier Hélios</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Lancer Training</t>
+          <t xml:space="preserve">Helios Lancer Training</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrenamiento de Lanceros Sublimes</t>
+          <t xml:space="preserve">Entrenamiento de Lancero Helios</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addestramento dei Lancieri esaltati</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Addestramento lancieri ardenti</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:35</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.entrainement_tireurs_glorifies</t>
+          <t xml:space="preserve">game.entrainement_de_tireur_helios</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
@@ -8373,22 +8378,22 @@
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entraînement de tireurs glorifiés</t>
+          <t xml:space="preserve">Entraînement de Tireur Hélios</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Marksman Training</t>
+          <t xml:space="preserve">Helios Marksman Training</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrenamiento de Tiradores Sublimes</t>
+          <t xml:space="preserve">Entrenamiento de Tirador Helios</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -8398,29 +8403,34 @@
       </c>
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addestramento dei Tiratori esaltati</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Addestramento tiratori Helios</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:35</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.entrainement_helios</t>
+          <t xml:space="preserve">game.entrainement_lanciers_glorifies</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
@@ -8430,59 +8440,54 @@
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entraînement de {unit} Hélios</t>
+          <t xml:space="preserve">Entraînement de lanciers glorifiés</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helios {unit} Training</t>
+          <t xml:space="preserve">Exalted Lancer Training</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrenamiento de {unit} Helios</t>
+          <t xml:space="preserve">Entrenamiento de Lanceros Sublimes</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addestramento di {unit} Helios</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
-        </is>
-      </c>
-      <c r="J35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
+          <t xml:space="preserve">Addestramento lancieri esaltati</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:61</t>
+          <t xml:space="preserve">data.js:35</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.entrainement_infanterie_helios</t>
+          <t xml:space="preserve">game.entrainement_tireurs_glorifies</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
@@ -8492,22 +8497,22 @@
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entraînement d’Infanterie Hélios</t>
+          <t xml:space="preserve">Entraînement de tireurs glorifiés</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helios Infantry Training</t>
+          <t xml:space="preserve">Exalted Marksman Training</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1229)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrenamiento de Infantería Helios</t>
+          <t xml:space="preserve">Entrenamiento de Tiradores Sublimes</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -8517,34 +8522,29 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addestramento di Fanteria Helios</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
-        </is>
-      </c>
-      <c r="J36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forme élidée produite par le code pour l’infanterie</t>
+          <t xml:space="preserve">Addestramento tiratori esaltati</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:61</t>
+          <t xml:space="preserve">data.js:35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.escouade_feu</t>
+          <t xml:space="preserve">game.entrainement_helios</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Escouade de Feu</t>
+          <t xml:space="preserve">Entraînement de {unit} Hélios</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flame Squad</t>
+          <t xml:space="preserve">Helios {unit} Training</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Escuadrón de Llamas</t>
+          <t xml:space="preserve">Entrenamiento de {unit} Helios</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Squadra di Fiamme</t>
+          <t xml:space="preserve">Addestramento di {unit} Helios</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -8587,6 +8587,11 @@
           <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
         </is>
       </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
+        </is>
+      </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T11</t>
@@ -8594,14 +8599,14 @@
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:53</t>
+          <t xml:space="preserve">data.js:61</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.excursion_glorifiee</t>
+          <t xml:space="preserve">game.entrainement_infanterie_helios</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
@@ -8611,54 +8616,59 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excursion Glorifiée</t>
+          <t xml:space="preserve">Entraînement d’Infanterie Hélios</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Trek</t>
+          <t xml:space="preserve">Helios Infantry Training</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1229)</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excursión sublime</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Entrenamiento de Infantería Helios</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traversata esaltata</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Addestramento fanteria Helios</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forme élidée produite par le code pour l’infanterie</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:15</t>
+          <t xml:space="preserve">data.js:61</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.fleche_cristal</t>
+          <t xml:space="preserve">game.escouade_feu</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
@@ -8668,12 +8678,12 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flèche de Cristal</t>
+          <t xml:space="preserve">Escouade de Feu</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crystal Arrow</t>
+          <t xml:space="preserve">Flame Squad</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8683,22 +8693,22 @@
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flecha de Cristal</t>
+          <t xml:space="preserve">Escuadrón de Llamas</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freccia di Cristallo</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Squadra fiamma</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K39" s="0" t="inlineStr">
@@ -8708,14 +8718,14 @@
       </c>
       <c r="L39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:50</t>
+          <t xml:space="preserve">data.js:53</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.frappe_feu</t>
+          <t xml:space="preserve">game.excursion_glorifiee</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
@@ -8725,54 +8735,54 @@
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frappe de Feu</t>
+          <t xml:space="preserve">Excursion Glorifiée</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flame Strike</t>
+          <t xml:space="preserve">Exalted Trek</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ataque de Llamas</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Excursión sublime</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colpo di Fiamme</t>
+          <t xml:space="preserve">Traversata esaltata</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:48</t>
+          <t xml:space="preserve">data.js:15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.gants_brulants</t>
+          <t xml:space="preserve">game.fleche_cristal</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
@@ -8782,54 +8792,54 @@
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gants Brûlants</t>
+          <t xml:space="preserve">Flèche de Cristal</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Grips</t>
+          <t xml:space="preserve">Crystal Arrow</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empuñadura fundida</t>
+          <t xml:space="preserve">Flecha de Cristal</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impugnatura fusa</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Freccia di cristallo</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:29</t>
+          <t xml:space="preserve">data.js:50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.garde_brulante</t>
+          <t xml:space="preserve">game.frappe_feu</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
@@ -8839,22 +8849,22 @@
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garde Brûlante</t>
+          <t xml:space="preserve">Frappe de Feu</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Guard</t>
+          <t xml:space="preserve">Flame Strike</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guardia fundido</t>
+          <t xml:space="preserve">Ataque de Llamas</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -8864,29 +8874,29 @@
       </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guardia fusa</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Attacco fiamma</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:27</t>
+          <t xml:space="preserve">data.js:48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.garde_epaules_glorifie</t>
+          <t xml:space="preserve">game.gants_brulants</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
@@ -8896,37 +8906,37 @@
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garde-épaules Glorifié</t>
+          <t xml:space="preserve">Gants Brûlants</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Shoulderguard</t>
+          <t xml:space="preserve">Molten Grips</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hombrera sublime</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Empuñadura fundida</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spallaccio esaltato</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Morsa fusa</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K43" s="0" t="inlineStr">
@@ -8936,14 +8946,14 @@
       </c>
       <c r="L43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:15</t>
+          <t xml:space="preserve">data.js:29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.gardien_embrase</t>
+          <t xml:space="preserve">game.garde_brulante</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
@@ -8953,22 +8963,22 @@
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gardien Embrasé</t>
+          <t xml:space="preserve">Garde Brûlante</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blazing Guardian</t>
+          <t xml:space="preserve">Molten Guard</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guardián Ardiente</t>
+          <t xml:space="preserve">Guardia fundido</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -8978,29 +8988,29 @@
       </c>
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guardiano Ardente</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guardia fusa</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:49</t>
+          <t xml:space="preserve">data.js:27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.lames_brulantes</t>
+          <t xml:space="preserve">game.garde_epaules_glorifie</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
@@ -9010,37 +9020,37 @@
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lames Brûlantes</t>
+          <t xml:space="preserve">Garde-épaules Glorifié</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Blades</t>
+          <t xml:space="preserve">Exalted Shoulderguard</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espadas fundidas</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Hombrera sublime</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lame fuse</t>
+          <t xml:space="preserve">Spallaccio esaltato</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K45" s="0" t="inlineStr">
@@ -9050,14 +9060,14 @@
       </c>
       <c r="L45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:27</t>
+          <t xml:space="preserve">data.js:15</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.lance_brulante</t>
+          <t xml:space="preserve">game.gardien_embrase</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
@@ -9067,22 +9077,22 @@
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lance Brûlante</t>
+          <t xml:space="preserve">Gardien Embrasé</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Lance</t>
+          <t xml:space="preserve">Blazing Guardian</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lanza fundida</t>
+          <t xml:space="preserve">Guardián Ardiente</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -9092,29 +9102,29 @@
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lancia fusa</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guardiano ardente</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:28</t>
+          <t xml:space="preserve">data.js:49</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.lance_embrasee</t>
+          <t xml:space="preserve">game.infanterie_helios</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
@@ -9124,12 +9134,12 @@
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lance Embrasée</t>
+          <t xml:space="preserve">Infanterie Hélios</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blazing Lance</t>
+          <t xml:space="preserve">Helios Infantry</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -9139,7 +9149,7 @@
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lanza Ardiente</t>
+          <t xml:space="preserve">Infantería Helios</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -9149,12 +9159,17 @@
       </c>
       <c r="H47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lancia Ardente</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Fanteria Helios</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K47" s="0" t="inlineStr">
@@ -9164,14 +9179,14 @@
       </c>
       <c r="L47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:49</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.legion_feu</t>
+          <t xml:space="preserve">game.infanterie_de_premiers_secours_helios</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
@@ -9181,12 +9196,12 @@
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Légion de Feu</t>
+          <t xml:space="preserve">Infanterie de Premiers Secours Hélios</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flame Legion</t>
+          <t xml:space="preserve">Helios Infantry First Aid</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -9196,7 +9211,7 @@
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legión de Llamas</t>
+          <t xml:space="preserve">Primeros Auxilios de Infantería Helios</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -9206,12 +9221,17 @@
       </c>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legione di Fiamme</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Primo soccorso fanteria Helios</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K48" s="0" t="inlineStr">
@@ -9221,14 +9241,14 @@
       </c>
       <c r="L48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:56</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.manteau_glorifie</t>
+          <t xml:space="preserve">game.infanterie_de_soins_helios</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
@@ -9238,54 +9258,59 @@
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manteau Glorifié</t>
+          <t xml:space="preserve">Infanterie de Soins Hélios</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Mantle</t>
+          <t xml:space="preserve">Helios Infantry Healing</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manto sublime</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Curación de Infantería Helios</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantello esaltato</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guarigione fanteria Helios</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:17</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.mur_indomptable</t>
+          <t xml:space="preserve">game.lames_brulantes</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
@@ -9295,37 +9320,37 @@
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mur Indomptable</t>
+          <t xml:space="preserve">Lames Brûlantes</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indomitable Wall</t>
+          <t xml:space="preserve">Molten Blades</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muro Indomable</t>
+          <t xml:space="preserve">Espadas fundidas</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muro indomabile</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Lame fuse</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K50" s="0" t="inlineStr">
@@ -9335,14 +9360,14 @@
       </c>
       <c r="L50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:31</t>
+          <t xml:space="preserve">data.js:27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.phalange_meridienne</t>
+          <t xml:space="preserve">game.lance_brulante</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
@@ -9352,12 +9377,12 @@
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phalange Méridienne</t>
+          <t xml:space="preserve">Lance Brûlante</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meridian Phalanx</t>
+          <t xml:space="preserve">Molten Lance</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -9367,7 +9392,7 @@
       </c>
       <c r="F51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falange meridiana</t>
+          <t xml:space="preserve">Lanza fundida</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -9377,12 +9402,12 @@
       </c>
       <c r="H51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falange meridiana</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Lancia fusa</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K51" s="0" t="inlineStr">
@@ -9392,14 +9417,14 @@
       </c>
       <c r="L51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:31</t>
+          <t xml:space="preserve">data.js:28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.pique_glorifiee</t>
+          <t xml:space="preserve">game.lance_embrasee</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
@@ -9409,54 +9434,54 @@
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pique Glorifiée</t>
+          <t xml:space="preserve">Lance Embrasée</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Pike</t>
+          <t xml:space="preserve">Blazing Lance</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pica sublime</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Lanza Ardiente</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Picca esaltata</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Lancia ardente</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:16</t>
+          <t xml:space="preserve">data.js:49</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.place_forte_glorifiee</t>
+          <t xml:space="preserve">game.lancier_helios</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
@@ -9466,54 +9491,59 @@
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place Forte Glorifiée</t>
+          <t xml:space="preserve">Lancier Hélios</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Bastion</t>
+          <t xml:space="preserve">Helios Lancer</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bastión sublime</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Lancero Helios</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bastione esaltato</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Lancieri Helios</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:15</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.premiers_secours_infanterie_glorifiee</t>
+          <t xml:space="preserve">game.lancier_de_premiers_secours_helios</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
@@ -9523,54 +9553,59 @@
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premiers secours de l'Infanterie glorifiée</t>
+          <t xml:space="preserve">Lancier de Premiers Secours Hélios</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Infantry First Aid</t>
+          <t xml:space="preserve">Helios Lancer First Aid</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primeros Auxilios de Infantería Sublime</t>
+          <t xml:space="preserve">Primeros Auxilios de Lancero Helios</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primo soccorso della Fanteria esaltata</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Primo soccorso Lancieri Helios</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:34</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.premiers_secours_lanciers_glorifies</t>
+          <t xml:space="preserve">game.lancier_de_soins_helios</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
@@ -9580,22 +9615,22 @@
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premiers secours des lanciers glorifiés</t>
+          <t xml:space="preserve">Lancier de Soins Hélios</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Lancer First Aid</t>
+          <t xml:space="preserve">Helios Lancer Healing</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primeros Auxilios de Lanceros Sublimes</t>
+          <t xml:space="preserve">Curación de Lancero Helios</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -9605,29 +9640,34 @@
       </c>
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primo soccorso dei Lancieri esaltati</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guarigione lancieri ardenti</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:34</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.premiers_secours_tireurs_glorifies</t>
+          <t xml:space="preserve">game.legion_feu</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
@@ -9637,22 +9677,22 @@
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premiers secours des tireurs glorifiés</t>
+          <t xml:space="preserve">Légion de Feu</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Marksman First Aid</t>
+          <t xml:space="preserve">Flame Legion</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primeros Auxilios de Tiradores Sublimes</t>
+          <t xml:space="preserve">Legión de Llamas</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -9662,29 +9702,29 @@
       </c>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primo soccorso dei Tiratori esaltati</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Legione fiamma</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:34</t>
+          <t xml:space="preserve">data.js:56</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.protection_cristal</t>
+          <t xml:space="preserve">game.manteau_glorifie</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
@@ -9694,54 +9734,54 @@
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protection de Cristal</t>
+          <t xml:space="preserve">Manteau Glorifié</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crystal Protection</t>
+          <t xml:space="preserve">Exalted Mantle</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protección de Cristal</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
+          <t xml:space="preserve">Manto sublime</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protezione di Cristallo</t>
+          <t xml:space="preserve">Mantello esaltato</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:50</t>
+          <t xml:space="preserve">data.js:17</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.protection_feu</t>
+          <t xml:space="preserve">game.mur_indomptable</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
@@ -9751,54 +9791,54 @@
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protection de Feu</t>
+          <t xml:space="preserve">Mur Indomptable</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flame Protection</t>
+          <t xml:space="preserve">Indomitable Wall</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protección de Llamas</t>
+          <t xml:space="preserve">Muro Indomable</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protezione di Fiamme</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Muro indomito</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:48</t>
+          <t xml:space="preserve">data.js:31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.protege_bras_brulants</t>
+          <t xml:space="preserve">game.phalange_meridienne</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
@@ -9808,12 +9848,12 @@
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protège-bras Brûlants</t>
+          <t xml:space="preserve">Phalange Méridienne</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Vambrace</t>
+          <t xml:space="preserve">Meridian Phalanx</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9823,7 +9863,7 @@
       </c>
       <c r="F59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avambrazo fundido</t>
+          <t xml:space="preserve">Falange meridiana</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -9833,12 +9873,12 @@
       </c>
       <c r="H59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bracciale fuso</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Falange meridiana</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K59" s="0" t="inlineStr">
@@ -9848,14 +9888,14 @@
       </c>
       <c r="L59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:28</t>
+          <t xml:space="preserve">data.js:31</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.precision_brulante</t>
+          <t xml:space="preserve">game.pique_glorifiee</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
@@ -9865,37 +9905,37 @@
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Précision Brûlante</t>
+          <t xml:space="preserve">Pique Glorifiée</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Sharpshooting</t>
+          <t xml:space="preserve">Exalted Pike</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiro con precisión fundido</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Pica sublime</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiro di precisione fuso</t>
+          <t xml:space="preserve">Picca esaltata</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K60" s="0" t="inlineStr">
@@ -9905,14 +9945,14 @@
       </c>
       <c r="L60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:29</t>
+          <t xml:space="preserve">data.js:16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.soins_infanterie_glorifiee</t>
+          <t xml:space="preserve">game.place_forte_glorifiee</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
@@ -9922,37 +9962,37 @@
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soins de l'Infanterie glorifiée</t>
+          <t xml:space="preserve">Place Forte Glorifiée</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Infantry Healing</t>
+          <t xml:space="preserve">Exalted Bastion</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curación de Infantería Sublime</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
+          <t xml:space="preserve">Bastión sublime</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cura della Fanteria esaltata</t>
+          <t xml:space="preserve">Bastione esaltato</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K61" s="0" t="inlineStr">
@@ -9962,14 +10002,14 @@
       </c>
       <c r="L61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:33</t>
+          <t xml:space="preserve">data.js:15</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.soins_lanciers_glorifies</t>
+          <t xml:space="preserve">game.premiers_secours_infanterie_glorifiee</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
@@ -9979,12 +10019,12 @@
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soins des lanciers glorifiés</t>
+          <t xml:space="preserve">Premiers secours de l'Infanterie glorifiée</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Lancer Healing</t>
+          <t xml:space="preserve">Exalted Infantry First Aid</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -9994,22 +10034,22 @@
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curación de Lanceros Sublimes</t>
+          <t xml:space="preserve">Primeros Auxilios de Infantería Sublime</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cura dei Lancieri esaltati</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Primo soccorso fanteria esaltata</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr">
@@ -10019,14 +10059,14 @@
       </c>
       <c r="L62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:33</t>
+          <t xml:space="preserve">data.js:34</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.soins_tireurs_glorifies</t>
+          <t xml:space="preserve">game.premiers_secours_lanciers_glorifies</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
@@ -10036,12 +10076,12 @@
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soins des tireurs glorifiés</t>
+          <t xml:space="preserve">Premiers secours des lanciers glorifiés</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Marksman Healing</t>
+          <t xml:space="preserve">Exalted Lancer First Aid</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -10051,7 +10091,7 @@
       </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curación de Tiradores Sublimes</t>
+          <t xml:space="preserve">Primeros Auxilios de Lanceros Sublimes</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -10061,12 +10101,12 @@
       </c>
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cura dei Tiratori esaltati</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Primo soccorso lancieri esaltati</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K63" s="0" t="inlineStr">
@@ -10076,14 +10116,14 @@
       </c>
       <c r="L63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:33</t>
+          <t xml:space="preserve">data.js:34</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.tactiques_brulantes</t>
+          <t xml:space="preserve">game.premiers_secours_tireurs_glorifies</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
@@ -10093,12 +10133,12 @@
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tactiques Brûlantes</t>
+          <t xml:space="preserve">Premiers secours des tireurs glorifiés</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Tactics</t>
+          <t xml:space="preserve">Exalted Marksman First Aid</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -10108,7 +10148,7 @@
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tácticas fundidas</t>
+          <t xml:space="preserve">Primeros Auxilios de Tiradores Sublimes</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -10118,12 +10158,12 @@
       </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tattiche fuse</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Primo soccorso tiratori esaltati</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K64" s="0" t="inlineStr">
@@ -10133,14 +10173,14 @@
       </c>
       <c r="L64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:28</t>
+          <t xml:space="preserve">data.js:34</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.tenue_guerre_glorifiee</t>
+          <t xml:space="preserve">game.protection_cristal</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
@@ -10150,54 +10190,54 @@
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tenue de Guerre Glorifiée</t>
+          <t xml:space="preserve">Protection de Cristal</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted War Garb</t>
+          <t xml:space="preserve">Crystal Protection</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atuendo de guerra sublime</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Protección de Cristal</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tenuta da guerra esaltata</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Protezione di cristallo</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:17</t>
+          <t xml:space="preserve">data.js:50</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.tir_ardent</t>
+          <t xml:space="preserve">game.protection_feu</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
@@ -10207,22 +10247,22 @@
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tir Ardent</t>
+          <t xml:space="preserve">Protection de Feu</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starfire</t>
+          <t xml:space="preserve">Flame Protection</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuego de estrella</t>
+          <t xml:space="preserve">Protección de Llamas</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -10232,29 +10272,29 @@
       </c>
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuoco stellare</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Protezione fiamma</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:31</t>
+          <t xml:space="preserve">data.js:48</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.tir_brulant</t>
+          <t xml:space="preserve">game.protege_bras_brulants</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
@@ -10264,12 +10304,12 @@
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tir Brûlant</t>
+          <t xml:space="preserve">Protège-bras Brûlants</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Shot</t>
+          <t xml:space="preserve">Molten Vambrace</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -10279,7 +10319,7 @@
       </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disparo fundido</t>
+          <t xml:space="preserve">Avambrazo fundido</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -10289,12 +10329,12 @@
       </c>
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colpo fuso</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Braccio fuso</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K67" s="0" t="inlineStr">
@@ -10304,14 +10344,14 @@
       </c>
       <c r="L67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:29</t>
+          <t xml:space="preserve">data.js:28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.tomahawk_feu</t>
+          <t xml:space="preserve">game.precision_brulante</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
@@ -10321,22 +10361,22 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomahawk de Feu</t>
+          <t xml:space="preserve">Précision Brûlante</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flame Tomahawk</t>
+          <t xml:space="preserve">Molten Sharpshooting</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hacha de Llamas</t>
+          <t xml:space="preserve">Tiro con precisión fundido</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -10346,29 +10386,29 @@
       </c>
       <c r="H68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomahawk di Fiamme</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Tiro di precisione fuso</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:48</t>
+          <t xml:space="preserve">data.js:29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.tromblon_glorifie</t>
+          <t xml:space="preserve">game.soins_infanterie_glorifiee</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
@@ -10378,37 +10418,37 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tromblon Glorifié</t>
+          <t xml:space="preserve">Soins de l'Infanterie glorifiée</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Blunderbuss</t>
+          <t xml:space="preserve">Exalted Infantry Healing</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trabuco sublime</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Curación de Infantería Sublime</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1340 à 1356)</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trombone esaltato</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guarigione fanteria esaltata</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K69" s="0" t="inlineStr">
@@ -10418,14 +10458,14 @@
       </c>
       <c r="L69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:17</t>
+          <t xml:space="preserve">data.js:33</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.vision_cristal</t>
+          <t xml:space="preserve">game.soins_lanciers_glorifies</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
@@ -10435,22 +10475,22 @@
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vision de Cristal</t>
+          <t xml:space="preserve">Soins des lanciers glorifiés</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crystal Vision</t>
+          <t xml:space="preserve">Exalted Lancer Healing</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visión de Cristal</t>
+          <t xml:space="preserve">Curación de Lanceros Sublimes</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -10460,29 +10500,29 @@
       </c>
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visione di Cristallo</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guarigione lancieri esaltati</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:50</t>
+          <t xml:space="preserve">data.js:33</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.voile_glorifie</t>
+          <t xml:space="preserve">game.soins_tireurs_glorifies</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
@@ -10492,37 +10532,37 @@
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Voile Glorifié</t>
+          <t xml:space="preserve">Soins des tireurs glorifiés</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Veil</t>
+          <t xml:space="preserve">Exalted Marksman Healing</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velo sublime</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Curación de Tiradores Sublimes</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velo esaltato</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guarigione tiratori esaltati</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K71" s="0" t="inlineStr">
@@ -10532,14 +10572,14 @@
       </c>
       <c r="L71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:17</t>
+          <t xml:space="preserve">data.js:33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.helios</t>
+          <t xml:space="preserve">game.tactiques_brulantes</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
@@ -10549,22 +10589,22 @@
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{unit} Hélios</t>
+          <t xml:space="preserve">Tactiques Brûlantes</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helios {unit}</t>
+          <t xml:space="preserve">Molten Tactics</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{unit} Helios</t>
+          <t xml:space="preserve">Tácticas fundidas</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -10574,34 +10614,29 @@
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{unit} Helios</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
-        </is>
-      </c>
-      <c r="J72" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
+          <t xml:space="preserve">Tattiche fuse</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:59</t>
+          <t xml:space="preserve">data.js:28</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.premiers_secours_helios</t>
+          <t xml:space="preserve">game.tenue_guerre_glorifiee</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
@@ -10611,59 +10646,54 @@
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{unit} de Premiers Secours Hélios</t>
+          <t xml:space="preserve">Tenue de Guerre Glorifiée</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helios {unit} First Aid</t>
+          <t xml:space="preserve">Exalted War Garb</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primeros Auxilios de {unit} Helios</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Atuendo de guerra sublime</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primo Soccorso di {unit} Helios</t>
+          <t xml:space="preserve">Tenuta da guerra esaltata</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
-        </is>
-      </c>
-      <c r="J73" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:62</t>
+          <t xml:space="preserve">data.js:17</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.soins_helios</t>
+          <t xml:space="preserve">game.tir_ardent</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
@@ -10673,22 +10703,22 @@
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{unit} de Soins Hélios</t>
+          <t xml:space="preserve">Tir Ardent</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helios {unit} Healing</t>
+          <t xml:space="preserve">Starfire</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curación de {unit} Helios</t>
+          <t xml:space="preserve">Fuego de estrella</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -10698,34 +10728,29 @@
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cura di {unit} Helios</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
-        </is>
-      </c>
-      <c r="J74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
+          <t xml:space="preserve">Fuoco stellare</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:60</t>
+          <t xml:space="preserve">data.js:31</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.ecailles_brulantes</t>
+          <t xml:space="preserve">game.tir_brulant</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
@@ -10735,12 +10760,12 @@
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Écailles Brûlantes</t>
+          <t xml:space="preserve">Tir Brûlant</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molten Scales</t>
+          <t xml:space="preserve">Molten Shot</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -10750,7 +10775,7 @@
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Escamas fundidas</t>
+          <t xml:space="preserve">Disparo fundido</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -10760,12 +10785,12 @@
       </c>
       <c r="H75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scaglie fuse</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Colpo fuso</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K75" s="0" t="inlineStr">
@@ -10782,7 +10807,7 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.epauliere_glorifiee</t>
+          <t xml:space="preserve">game.tireur_helios</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
@@ -10792,79 +10817,84 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Épaulière Glorifiée</t>
+          <t xml:space="preserve">Tireur Hélios</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Pauldron</t>
+          <t xml:space="preserve">Helios Marksman</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espaldarón sublime</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
+          <t xml:space="preserve">Tirador Helios</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spalliera esaltata</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Tiratori Helios</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:16</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.accelerateurs</t>
+          <t xml:space="preserve">game.tireur_de_premiers_secours_helios</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accélérateurs</t>
+          <t xml:space="preserve">Tireur de Premiers Secours Hélios</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Speedups</t>
+          <t xml:space="preserve">Helios Marksman First Aid</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — WOSForge</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aceleradores</t>
+          <t xml:space="preserve">Primeros Auxilios de Tirador Helios</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -10874,54 +10904,59 @@
       </c>
       <c r="H77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceleratori</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Primo soccorso tiratori Helios</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaudière, T11, T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:149, t11.js:131, t12.js:370</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.acier</t>
+          <t xml:space="preserve">game.tireur_de_soins_helios</t>
         </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acier</t>
+          <t xml:space="preserve">Tireur de Soins Hélios</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel</t>
+          <t xml:space="preserve">Helios Marksman Healing</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acero</t>
+          <t xml:space="preserve">Curación de Tirador Helios</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -10931,54 +10966,59 @@
       </c>
       <c r="H78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acciaio</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guarigione tiratori Helios</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom composé par le code (unité + recherche)</t>
         </is>
       </c>
       <c r="K78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11, T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">t11.js:126, t12.js:353, t12.js:365</t>
+          <t xml:space="preserve">t11.js</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.alliage_renforce</t>
+          <t xml:space="preserve">game.tomahawk_feu</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alliage renforcé</t>
+          <t xml:space="preserve">Tomahawk de Feu</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hardened Alloy</t>
+          <t xml:space="preserve">Flame Tomahawk</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aleación endurecida</t>
+          <t xml:space="preserve">Hacha de Llamas</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -10988,111 +11028,111 @@
       </c>
       <c r="H79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lega temprata</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Tomahawk fiamma</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Équipement</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:155</t>
+          <t xml:space="preserve">data.js:48</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.ambre_lunaire</t>
+          <t xml:space="preserve">game.tromblon_glorifie</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ambre lunaire</t>
+          <t xml:space="preserve">Tromblon Glorifié</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunar Amber</t>
+          <t xml:space="preserve">Exalted Blunderbuss</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ámbar lunar</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Trabuco sublime</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ambra lunare</t>
+          <t xml:space="preserve">Trombone esaltato</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Équipement</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:155</t>
+          <t xml:space="preserve">data.js:17</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.bois</t>
+          <t xml:space="preserve">game.vision_cristal</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bois</t>
+          <t xml:space="preserve">Vision de Cristal</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wood</t>
+          <t xml:space="preserve">Crystal Vision</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madera</t>
+          <t xml:space="preserve">Visión de Cristal</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -11102,111 +11142,111 @@
       </c>
       <c r="H81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legno</t>
-        </is>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Visione di cristallo</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaudière, T11, T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:149, t11.js:128, t12.js:367</t>
+          <t xml:space="preserve">data.js:50</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.charbon</t>
+          <t xml:space="preserve">game.voile_glorifie</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charbon</t>
+          <t xml:space="preserve">Voile Glorifié</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coal</t>
+          <t xml:space="preserve">Exalted Veil</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carbón</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Velo sublime</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carbone</t>
+          <t xml:space="preserve">Velo esaltato</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaudière, T11, T12</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:149, t11.js:129, t12.js:368</t>
+          <t xml:space="preserve">data.js:17</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.cristaux_feu</t>
+          <t xml:space="preserve">game.helios</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristaux de feu</t>
+          <t xml:space="preserve">{unit} Hélios</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fire Crystal</t>
+          <t xml:space="preserve">Helios {unit}</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristal de Fuego</t>
+          <t xml:space="preserve">{unit} Helios</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -11216,7 +11256,7 @@
       </c>
       <c r="H83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristallo di Fuoco</t>
+          <t xml:space="preserve">{unit} Helios</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -11224,46 +11264,51 @@
           <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
         </is>
       </c>
+      <c r="J83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
+        </is>
+      </c>
       <c r="K83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaudière</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:149</t>
+          <t xml:space="preserve">data.js:59</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.cristaux_raffines</t>
+          <t xml:space="preserve">game.premiers_secours_helios</t>
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristaux raffinés</t>
+          <t xml:space="preserve">{unit} de Premiers Secours Hélios</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refined Fire Crystal</t>
+          <t xml:space="preserve">Helios {unit} First Aid</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristal de fuego refinado</t>
+          <t xml:space="preserve">Primeros Auxilios de {unit} Helios</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -11273,7 +11318,7 @@
       </c>
       <c r="H84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristallo di Fuoco raffinato</t>
+          <t xml:space="preserve">Primo Soccorso di {unit} Helios</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -11281,46 +11326,51 @@
           <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
         </is>
       </c>
+      <c r="J84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
+        </is>
+      </c>
       <c r="K84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaudière, T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:149, t12.js:352, t12.js:364</t>
+          <t xml:space="preserve">data.js:62</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.fer</t>
+          <t xml:space="preserve">game.soins_helios</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fer</t>
+          <t xml:space="preserve">{unit} de Soins Hélios</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iron</t>
+          <t xml:space="preserve">Helios {unit} Healing</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
         </is>
       </c>
       <c r="F85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hierro</t>
+          <t xml:space="preserve">Curación de {unit} Helios</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -11330,7 +11380,7 @@
       </c>
       <c r="H85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ferro</t>
+          <t xml:space="preserve">Cura di {unit} Helios</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -11338,46 +11388,51 @@
           <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
         </is>
       </c>
+      <c r="J85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garder les variables entre accolades : {unit}</t>
+        </is>
+      </c>
       <c r="K85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaudière, T11, T12</t>
+          <t xml:space="preserve">T11</t>
         </is>
       </c>
       <c r="L85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:149, t11.js:130, t12.js:369</t>
+          <t xml:space="preserve">data.js:60</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.fragment_cristal_ardent</t>
+          <t xml:space="preserve">game.ecailles_brulantes</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fragment de Cristal Ardent</t>
+          <t xml:space="preserve">Écailles Brûlantes</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fire Crystal Shard</t>
+          <t xml:space="preserve">Molten Scales</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1242 à 1269)</t>
         </is>
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fragmento de Cristal de Fuego</t>
+          <t xml:space="preserve">Escamas fundidas</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -11387,86 +11442,86 @@
       </c>
       <c r="H86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frammento di Cristallo di Fuoco</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Scaglie fuse</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11, T12</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">t11.js:125, t12.js:351, t12.js:363</t>
+          <t xml:space="preserve">data.js:29</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.guides_talisman</t>
+          <t xml:space="preserve">game.epauliere_glorifiee</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ressource</t>
+          <t xml:space="preserve">Recherche / pièce T11-T12</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guides de talisman</t>
+          <t xml:space="preserve">Épaulière Glorifiée</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charm Guide</t>
+          <t xml:space="preserve">Exalted Pauldron</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
       <c r="F87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guía de talismanes</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+          <t xml:space="preserve">Espaldarón sublime</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR (aucune source espagnole publique), modèle du jeu « … sublime »</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guida al talismano</t>
+          <t xml:space="preserve">Spalliera esaltata</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Déduit des noms officiels EN et FR, sur le modèle du jeu italien (« … esaltato »)</t>
         </is>
       </c>
       <c r="K87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talismans</t>
+          <t xml:space="preserve">T12</t>
         </is>
       </c>
       <c r="L87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:223</t>
+          <t xml:space="preserve">data.js:16</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.nourriture</t>
+          <t xml:space="preserve">game.accelerateurs</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
@@ -11476,22 +11531,22 @@
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nourriture</t>
+          <t xml:space="preserve">Accélérateurs</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meat</t>
+          <t xml:space="preserve">Speedups</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1273) : la nourriture s’appelle Meat</t>
+          <t xml:space="preserve">Officiel — WOSForge</t>
         </is>
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carne</t>
+          <t xml:space="preserve">Aceleradores</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -11501,29 +11556,29 @@
       </c>
       <c r="H88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carne</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Acceleratori</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaudière</t>
+          <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
       <c r="L88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:149</t>
+          <t xml:space="preserve">app.js:149, t11.js:131, t12.js:370</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.plans_conception</t>
+          <t xml:space="preserve">game.acier</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
@@ -11533,12 +11588,12 @@
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plans de conception</t>
+          <t xml:space="preserve">Acier</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Design Plans</t>
+          <t xml:space="preserve">Steel</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -11548,7 +11603,7 @@
       </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planos de diseño</t>
+          <t xml:space="preserve">Acero</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -11558,29 +11613,29 @@
       </c>
       <c r="H89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progetti di design</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Acciaio</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Équipement</t>
+          <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
       <c r="L89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:155</t>
+          <t xml:space="preserve">t11.js:126, t12.js:353, t12.js:365</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.plans_talisman</t>
+          <t xml:space="preserve">game.alliage_renforce</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
@@ -11590,12 +11645,12 @@
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plans de talisman</t>
+          <t xml:space="preserve">Alliage renforcé</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charm Design</t>
+          <t xml:space="preserve">Hardened Alloy</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -11605,7 +11660,7 @@
       </c>
       <c r="F90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planos de talismán</t>
+          <t xml:space="preserve">Aleación endurecida</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -11615,29 +11670,29 @@
       </c>
       <c r="H90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progetto del talismano</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Lega rinforzata</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talismans</t>
+          <t xml:space="preserve">Équipement</t>
         </is>
       </c>
       <c r="L90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:224</t>
+          <t xml:space="preserve">app.js:155</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.secrets_talisman</t>
+          <t xml:space="preserve">game.ambre_lunaire</t>
         </is>
       </c>
       <c r="B91" s="0" t="inlineStr">
@@ -11647,12 +11702,12 @@
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secrets de talisman</t>
+          <t xml:space="preserve">Ambre lunaire</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charm Secrets</t>
+          <t xml:space="preserve">Lunar Amber</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -11662,7 +11717,7 @@
       </c>
       <c r="F91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secretos de talismanes</t>
+          <t xml:space="preserve">Ámbar lunar</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -11672,29 +11727,29 @@
       </c>
       <c r="H91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segreti del talismano</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Ambra lunare</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talismans</t>
+          <t xml:space="preserve">Équipement</t>
         </is>
       </c>
       <c r="L91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:225</t>
+          <t xml:space="preserve">app.js:155</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.solution_polissage</t>
+          <t xml:space="preserve">game.bois</t>
         </is>
       </c>
       <c r="B92" s="0" t="inlineStr">
@@ -11704,12 +11759,12 @@
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solution de polissage</t>
+          <t xml:space="preserve">Bois</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polishing Solution</t>
+          <t xml:space="preserve">Wood</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -11719,7 +11774,7 @@
       </c>
       <c r="F92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solución pulidora</t>
+          <t xml:space="preserve">Madera</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -11729,29 +11784,29 @@
       </c>
       <c r="H92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soluzione lucidante</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Legna</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Équipement</t>
+          <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
       <c r="L92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">app.js:155</t>
+          <t xml:space="preserve">app.js:149, t11.js:128, t12.js:367</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.viande</t>
+          <t xml:space="preserve">game.charbon</t>
         </is>
       </c>
       <c r="B93" s="0" t="inlineStr">
@@ -11761,12 +11816,12 @@
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viande</t>
+          <t xml:space="preserve">Charbon</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meat</t>
+          <t xml:space="preserve">Coal</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -11776,7 +11831,7 @@
       </c>
       <c r="F93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carne</t>
+          <t xml:space="preserve">Carbón</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -11786,54 +11841,54 @@
       </c>
       <c r="H93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carne</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Carbone</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11, T12</t>
+          <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
       <c r="L93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">t11.js:127, t12.js:366</t>
+          <t xml:space="preserve">app.js:149, t11.js:129, t12.js:368</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.attaque</t>
+          <t xml:space="preserve">game.cristaux_feu</t>
         </is>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statistique</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Cristaux de feu</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attack</t>
+          <t xml:space="preserve">Fire Crystal</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ataque</t>
+          <t xml:space="preserve">Cristal de Fuego</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -11843,54 +11898,54 @@
       </c>
       <c r="H94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attacco</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Cristallo di Fuoco</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non vu à l’écran (données)</t>
+          <t xml:space="preserve">Chaudière</t>
         </is>
       </c>
       <c r="L94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:24</t>
+          <t xml:space="preserve">app.js:149</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.capacite_deploiement</t>
+          <t xml:space="preserve">game.cristaux_raffines</t>
         </is>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statistique</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacité de déploiement</t>
+          <t xml:space="preserve">Cristaux raffinés</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troops Deployment Capacity</t>
+          <t xml:space="preserve">Refined Fire Crystal</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacidad de despliegue de tropas</t>
+          <t xml:space="preserve">Cristal de fuego refinado</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -11900,54 +11955,54 @@
       </c>
       <c r="H95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacità di schieramento</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Cristallo di Fuoco raffinato</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">Chaudière, T12</t>
         </is>
       </c>
       <c r="L95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:24</t>
+          <t xml:space="preserve">app.js:149, t12.js:352, t12.js:364</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.capacite_deploiement_troupes</t>
+          <t xml:space="preserve">game.fer</t>
         </is>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statistique</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacité de déploiement des troupes</t>
+          <t xml:space="preserve">Fer</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troops Deployment Capacity</t>
+          <t xml:space="preserve">Iron</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacidad de despliegue de tropas</t>
+          <t xml:space="preserve">Hierro</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -11957,54 +12012,54 @@
       </c>
       <c r="H96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacità di schieramento</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Ferro</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">Chaudière, T11, T12</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">t12.js:293</t>
+          <t xml:space="preserve">app.js:149, t11.js:130, t12.js:369</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.defense</t>
+          <t xml:space="preserve">game.fragment_cristal_ardent</t>
         </is>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statistique</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Défense</t>
+          <t xml:space="preserve">Fragment de Cristal Ardent</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Defense</t>
+          <t xml:space="preserve">Fire Crystal Shard</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Defensa</t>
+          <t xml:space="preserve">Fragmento de Cristal de Fuego</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -12014,54 +12069,54 @@
       </c>
       <c r="H97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Difesa</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Frammento del Cristallo di Fuoco</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non vu à l’écran (données)</t>
+          <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
       <c r="L97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:24</t>
+          <t xml:space="preserve">t11.js:125, t12.js:351, t12.js:363</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.letalite</t>
+          <t xml:space="preserve">game.guides_talisman</t>
         </is>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statistique</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Létalité</t>
+          <t xml:space="preserve">Guides de talisman</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lethality</t>
+          <t xml:space="preserve">Charm Guide</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Letalidad</t>
+          <t xml:space="preserve">Guía de talismanes</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -12071,54 +12126,54 @@
       </c>
       <c r="H98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Letalità</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Guida ai talismani</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non vu à l’écran (données)</t>
+          <t xml:space="preserve">Talismans</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:24</t>
+          <t xml:space="preserve">app.js:223</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.puissance</t>
+          <t xml:space="preserve">game.nourriture</t>
         </is>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statistique</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puissance</t>
+          <t xml:space="preserve">Nourriture</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power</t>
+          <t xml:space="preserve">Meat</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1273) : la nourriture s’appelle Meat</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poder</t>
+          <t xml:space="preserve">Carne</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -12128,54 +12183,54 @@
       </c>
       <c r="H99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Potenza</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Carne</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">Chaudière</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">t12.js:309</t>
+          <t xml:space="preserve">app.js:149</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.sante</t>
+          <t xml:space="preserve">game.plans_conception</t>
         </is>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statistique</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santé</t>
+          <t xml:space="preserve">Plans de conception</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health</t>
+          <t xml:space="preserve">Design Plans</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salud</t>
+          <t xml:space="preserve">Planos de diseño</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -12185,54 +12240,54 @@
       </c>
       <c r="H100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salute</t>
-        </is>
-      </c>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Progetti</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non vu à l’écran (données)</t>
+          <t xml:space="preserve">Équipement</t>
         </is>
       </c>
       <c r="L100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:24</t>
+          <t xml:space="preserve">app.js:155</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.infanterie</t>
+          <t xml:space="preserve">game.plans_talisman</t>
         </is>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troupe</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infanterie</t>
+          <t xml:space="preserve">Plans de talisman</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infantry</t>
+          <t xml:space="preserve">Charm Design</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infantería</t>
+          <t xml:space="preserve">Planos de talismán</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -12242,54 +12297,54 @@
       </c>
       <c r="H101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fanteria</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Progetto talismano</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11, T12</t>
+          <t xml:space="preserve">Talismans</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">index.html:83, app.js:151, app.js:152, app.js:153, app.js:199, app.js:204, app.js:206, data.js:8, data.js:46, t12.js:220</t>
+          <t xml:space="preserve">app.js:224</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.infanterie_glorifiee</t>
+          <t xml:space="preserve">game.secrets_talisman</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troupe</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infanterie Glorifiée</t>
+          <t xml:space="preserve">Secrets de talisman</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Infantry</t>
+          <t xml:space="preserve">Charm Secrets</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infantería sublime</t>
+          <t xml:space="preserve">Secretos de talismanes</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -12299,54 +12354,54 @@
       </c>
       <c r="H102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fanteria esaltata</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Segreti dei talismani</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">Talismans</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:12</t>
+          <t xml:space="preserve">app.js:225</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.lancier</t>
+          <t xml:space="preserve">game.solution_polissage</t>
         </is>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troupe</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lancier</t>
+          <t xml:space="preserve">Solution de polissage</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lancer</t>
+          <t xml:space="preserve">Polishing Solution</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lancero</t>
+          <t xml:space="preserve">Solución pulidora</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -12356,54 +12411,54 @@
       </c>
       <c r="H103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lanciere</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Soluzione lucidante</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11, T12, Talismans</t>
+          <t xml:space="preserve">Équipement</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">index.html:84, app.js:151, app.js:152, app.js:153, app.js:199, app.js:204, app.js:206, data.js:8, data.js:46, t12.js:220</t>
+          <t xml:space="preserve">app.js:155</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.lancier_glorifie</t>
+          <t xml:space="preserve">game.viande</t>
         </is>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troupe</t>
+          <t xml:space="preserve">Ressource</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lancier Glorifié</t>
+          <t xml:space="preserve">Viande</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exalted Lancer</t>
+          <t xml:space="preserve">Meat</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1270 à 1283)</t>
         </is>
       </c>
       <c r="F104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lancero sublime</t>
+          <t xml:space="preserve">Carne</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -12413,44 +12468,44 @@
       </c>
       <c r="H104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lanciere esaltato</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Carne</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T12</t>
+          <t xml:space="preserve">T11, T12</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">data.js:12</t>
+          <t xml:space="preserve">t11.js:127, t12.js:366</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">game.tireur</t>
+          <t xml:space="preserve">game.attaque</t>
         </is>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troupe</t>
+          <t xml:space="preserve">Statistique</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tireur</t>
+          <t xml:space="preserve">Attaque</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marksman</t>
+          <t xml:space="preserve">Attack</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -12460,7 +12515,7 @@
       </c>
       <c r="F105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tirador</t>
+          <t xml:space="preserve">Ataque</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -12470,84 +12525,711 @@
       </c>
       <c r="H105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiratore</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
+          <t xml:space="preserve">Attacco</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
         </is>
       </c>
       <c r="K105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T11, T12</t>
+          <t xml:space="preserve">Non vu à l’écran (données)</t>
         </is>
       </c>
       <c r="L105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">index.html:85, data.js:8, data.js:46, t12.js:220</t>
+          <t xml:space="preserve">data.js:24</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">game.capacite_deploiement</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistique</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacité de déploiement</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troops Deployment Capacity</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+        </is>
+      </c>
+      <c r="F106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacidad de despliegue de tropas</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacità Schieramento Truppe</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T12</t>
+        </is>
+      </c>
+      <c r="L106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data.js:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.capacite_deploiement_troupes</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistique</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacité de déploiement des troupes</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troops Deployment Capacity</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+        </is>
+      </c>
+      <c r="F107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacidad de despliegue de tropas</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacità Schieramento Truppe</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T12</t>
+        </is>
+      </c>
+      <c r="L107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t12.js:293</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.defense</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistique</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Défense</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defense</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+        </is>
+      </c>
+      <c r="F108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defensa</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Difesa</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non vu à l’écran (données)</t>
+        </is>
+      </c>
+      <c r="L108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data.js:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.letalite</t>
+        </is>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistique</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Létalité</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lethality</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+        </is>
+      </c>
+      <c r="F109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Letalidad</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Letalità</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non vu à l’écran (données)</t>
+        </is>
+      </c>
+      <c r="L109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data.js:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.puissance</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistique</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Puissance</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+        </is>
+      </c>
+      <c r="F110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poder</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Potere</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T12</t>
+        </is>
+      </c>
+      <c r="L110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t12.js:309</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.sante</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistique</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santé</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+        </is>
+      </c>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salud</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salute</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non vu à l’écran (données)</t>
+        </is>
+      </c>
+      <c r="L111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data.js:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.infanterie</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troupe</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infanterie</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infantry</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+        </is>
+      </c>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infantería</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fanteria</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des captures (le jeu italien emploie « fanteria », « lancieri », « tiratori »)</t>
+        </is>
+      </c>
+      <c r="K112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T11, T12</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">index.html:83, app.js:151, app.js:152, app.js:153, app.js:199, app.js:204, app.js:206, data.js:8, data.js:46, t12.js:220</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.infanterie_glorifiee</t>
+        </is>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troupe</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infanterie Glorifiée</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exalted Infantry</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+        </is>
+      </c>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infantería sublime</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fanteria esaltata</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T12</t>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data.js:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.lancier</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troupe</t>
+        </is>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancier</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancer</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+        </is>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancero</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancieri</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des captures (le jeu italien emploie « fanteria », « lancieri », « tiratori »)</t>
+        </is>
+      </c>
+      <c r="K114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T11, T12, Talismans</t>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">index.html:84, app.js:151, app.js:152, app.js:153, app.js:199, app.js:204, app.js:206, data.js:8, data.js:46, t12.js:220</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.lancier_glorifie</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troupe</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancier Glorifié</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exalted Lancer</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
+        </is>
+      </c>
+      <c r="F115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancero sublime</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lancieri esaltati</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T12</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data.js:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">game.tireur</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troupe</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tireur</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marksman</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1211 à 1240)</t>
+        </is>
+      </c>
+      <c r="F116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tirador</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
+        </is>
+      </c>
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiratori</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déduit des captures (le jeu italien emploie « fanteria », « lancieri », « tiratori »)</t>
+        </is>
+      </c>
+      <c r="K116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T11, T12</t>
+        </is>
+      </c>
+      <c r="L116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">index.html:85, data.js:8, data.js:46, t12.js:220</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">game.tireur_glorifie</t>
         </is>
       </c>
-      <c r="B106" s="0" t="inlineStr">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Troupe</t>
         </is>
       </c>
-      <c r="C106" s="0" t="inlineStr">
+      <c r="C117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Tireur Glorifié</t>
         </is>
       </c>
-      <c r="D106" s="0" t="inlineStr">
+      <c r="D117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Exalted Marksman</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Officiel — capture du jeu en anglais (IMG_1055 à 1075)</t>
         </is>
       </c>
-      <c r="F106" s="0" t="inlineStr">
+      <c r="F117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Tirador sublime</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Officiel — capture du jeu en espagnol (IMG_1284 à 1339)</t>
         </is>
       </c>
-      <c r="H106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiratore esaltato</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposition — à vérifier en jeu (traduite depuis les noms officiels EN/FR)</t>
-        </is>
-      </c>
-      <c r="K106" s="0" t="inlineStr">
+      <c r="H117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiratori esaltati</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Officiel — capture du jeu en italien (IMG_1358 à 1433)</t>
+        </is>
+      </c>
+      <c r="K117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">T12</t>
         </is>
       </c>
-      <c r="L106" s="0" t="inlineStr">
+      <c r="L117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">data.js:12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L106"/>
+  <autoFilter ref="A3:L117"/>
 </worksheet>
 </file>
 

--- a/i18n/lexique.xlsx
+++ b/i18n/lexique.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipaggiamento Capo</t>
+          <t xml:space="preserve">Equipaggiamento del Capo</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">

--- a/i18n/lexique.xlsx
+++ b/i18n/lexique.xlsx
@@ -1360,22 +1360,22 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outil communautaire non officiel · Les données V1 sont isolées et versionnées pour audit.</t>
+          <t xml:space="preserve">Outil communautaire non officiel</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unofficial community tool · V1 data is isolated and versioned for auditing.</t>
+          <t xml:space="preserve">Unofficial community tool</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herramienta comunitaria no oficial · Los datos V1 están aislados y versionados para auditoría.</t>
+          <t xml:space="preserve">Herramienta comunitaria no oficial</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strumento non ufficiale della community · I dati V1 sono isolati e versionati per la verifica.</t>
+          <t xml:space="preserve">Strumento non ufficiale della community</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
